--- a/Sindhi Muslim/Result Sheet/Monthly Test - Oct 2024.xlsx
+++ b/Sindhi Muslim/Result Sheet/Monthly Test - Oct 2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Result Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4EBF02-A6D2-46F7-BDD0-32A7F3F05FDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009C673E-0509-41BA-9675-F426F632532A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="8" xr2:uid="{A3810461-FCAA-4427-95C3-213E25AAD5DA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{A3810461-FCAA-4427-95C3-213E25AAD5DA}"/>
   </bookViews>
   <sheets>
     <sheet name="ECE (ROSE)" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="601">
   <si>
     <t>GOVERNMENT HIGH SCHOOL SINDHI JAMAAT CO-OPERATIVE HOUSING SOCIETY</t>
   </si>
@@ -1846,6 +1846,9 @@
   </si>
   <si>
     <t>Sara</t>
+  </si>
+  <si>
+    <t>Activity</t>
   </si>
 </sst>
 </file>
@@ -2053,7 +2056,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2141,6 +2144,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2179,15 +2188,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2539,95 +2539,95 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
     </row>
     <row r="2" spans="1:18" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="31"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
     </row>
     <row r="3" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="32" t="s">
+      <c r="C3" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="36" t="s">
+      <c r="E3" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="O3" s="32" t="s">
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="32" t="s">
+      <c r="P3" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" s="32" t="s">
+      <c r="Q3" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="R3" s="32" t="s">
+      <c r="R3" s="34" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="47.25" x14ac:dyDescent="0.2">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="34"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="36"/>
       <c r="F4" s="2" t="s">
         <v>8</v>
       </c>
@@ -2655,17 +2655,17 @@
       <c r="N4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O4" s="32"/>
-      <c r="P4" s="32"/>
-      <c r="Q4" s="32"/>
-      <c r="R4" s="32"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="34"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="32"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="35"/>
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="37"/>
       <c r="F5" s="3">
         <v>5</v>
       </c>
@@ -2696,9 +2696,9 @@
       <c r="O5" s="3">
         <v>60</v>
       </c>
-      <c r="P5" s="32"/>
-      <c r="Q5" s="32"/>
-      <c r="R5" s="32"/>
+      <c r="P5" s="34"/>
+      <c r="Q5" s="34"/>
+      <c r="R5" s="34"/>
     </row>
     <row r="6" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
@@ -5608,7 +5608,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A3CBCD-1F78-4D0E-8FCF-9D808A1A2F00}">
-  <dimension ref="A1:S63"/>
+  <dimension ref="A1:T63"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.140625" style="1" bestFit="1" customWidth="1"/>
@@ -5616,106 +5616,109 @@
     <col min="3" max="3" width="9.140625" style="1"/>
     <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="9.140625" style="1"/>
-    <col min="6" max="18" width="6.7109375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="15.85546875" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="19" width="6.7109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="15.85546875" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
-    </row>
-    <row r="2" spans="1:19" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+    <row r="1" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+    </row>
+    <row r="2" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="31"/>
-      <c r="S2" s="31"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
+      <c r="T2" s="33"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A3" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="32" t="s">
+      <c r="C3" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="36" t="s">
+      <c r="E3" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="O3" s="32" t="s">
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="38"/>
+      <c r="P3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="32" t="s">
+      <c r="Q3" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" s="32" t="s">
+      <c r="R3" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="R3" s="32" t="s">
+      <c r="S3" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="S3" s="32" t="s">
+      <c r="T3" s="34" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="47.25" x14ac:dyDescent="0.2">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="34"/>
+    <row r="4" spans="1:20" ht="47.25" x14ac:dyDescent="0.2">
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="36"/>
       <c r="F4" s="2" t="s">
         <v>8</v>
       </c>
@@ -5723,58 +5726,61 @@
         <v>9</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>10</v>
+        <v>279</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>120</v>
+        <v>182</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="M4" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O4" s="32"/>
-      <c r="P4" s="32"/>
-      <c r="Q4" s="32"/>
-      <c r="R4" s="32"/>
-      <c r="S4" s="32"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A5" s="32"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="35"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="34"/>
+      <c r="S4" s="34"/>
+      <c r="T4" s="34"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="37"/>
       <c r="F5" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G5" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="H5" s="3">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="I5" s="3">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="J5" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="K5" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="L5" s="3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M5" s="3">
         <v>10</v>
@@ -5783,37 +5789,41 @@
         <v>10</v>
       </c>
       <c r="O5" s="3">
-        <v>375</v>
-      </c>
-      <c r="P5" s="32"/>
-      <c r="Q5" s="32"/>
-      <c r="R5" s="32"/>
-      <c r="S5" s="32"/>
-    </row>
-    <row r="6" spans="1:19" ht="21" x14ac:dyDescent="0.35">
-      <c r="A6" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="P5" s="3">
+        <v>70</v>
+      </c>
+      <c r="Q5" s="34"/>
+      <c r="R5" s="34"/>
+      <c r="S5" s="34"/>
+      <c r="T5" s="34"/>
+    </row>
+    <row r="6" spans="1:20" ht="21" x14ac:dyDescent="0.35">
+      <c r="A6" s="39" t="s">
         <v>183</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="38"/>
-      <c r="Q6" s="38"/>
-      <c r="R6" s="38"/>
-      <c r="S6" s="39"/>
-    </row>
-    <row r="7" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="40"/>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="40"/>
+      <c r="S6" s="40"/>
+      <c r="T6" s="41"/>
+    </row>
+    <row r="7" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>1</v>
       </c>
@@ -5829,22 +5839,51 @@
       <c r="E7" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
+      <c r="F7" s="4">
+        <v>5</v>
+      </c>
+      <c r="G7" s="4">
+        <v>5</v>
+      </c>
+      <c r="H7" s="4">
+        <v>4</v>
+      </c>
+      <c r="I7" s="4">
+        <v>4</v>
+      </c>
+      <c r="J7" s="4">
+        <v>5</v>
+      </c>
+      <c r="K7" s="4">
+        <v>4</v>
+      </c>
+      <c r="L7" s="4">
+        <v>8</v>
+      </c>
+      <c r="M7" s="4">
+        <v>8</v>
+      </c>
+      <c r="N7" s="4">
+        <v>10</v>
+      </c>
+      <c r="O7" s="4">
+        <v>8</v>
+      </c>
+      <c r="P7" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q7" s="4">
+        <f>SUM(F7:O7)</f>
+        <v>61</v>
+      </c>
+      <c r="R7" s="4">
+        <f>Q7/P7*100</f>
+        <v>87.142857142857139</v>
+      </c>
       <c r="S7" s="4"/>
-    </row>
-    <row r="8" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T7" s="4"/>
+    </row>
+    <row r="8" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>2</v>
       </c>
@@ -5860,22 +5899,51 @@
       <c r="E8" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
+      <c r="F8" s="4">
+        <v>5</v>
+      </c>
+      <c r="G8" s="4">
+        <v>4</v>
+      </c>
+      <c r="H8" s="4">
+        <v>4</v>
+      </c>
+      <c r="I8" s="4">
+        <v>4</v>
+      </c>
+      <c r="J8" s="4">
+        <v>5</v>
+      </c>
+      <c r="K8" s="4">
+        <v>5</v>
+      </c>
+      <c r="L8" s="4">
+        <v>8</v>
+      </c>
+      <c r="M8" s="4">
+        <v>8</v>
+      </c>
+      <c r="N8" s="4">
+        <v>9</v>
+      </c>
+      <c r="O8" s="4">
+        <v>10</v>
+      </c>
+      <c r="P8" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q8" s="4">
+        <f t="shared" ref="Q8:Q31" si="0">SUM(F8:O8)</f>
+        <v>62</v>
+      </c>
+      <c r="R8" s="4">
+        <f t="shared" ref="R8:R31" si="1">Q8/P8*100</f>
+        <v>88.571428571428569</v>
+      </c>
       <c r="S8" s="4"/>
-    </row>
-    <row r="9" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T8" s="4"/>
+    </row>
+    <row r="9" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>3</v>
       </c>
@@ -5891,22 +5959,51 @@
       <c r="E9" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
+      <c r="F9" s="4">
+        <v>5</v>
+      </c>
+      <c r="G9" s="4">
+        <v>5</v>
+      </c>
+      <c r="H9" s="4">
+        <v>5</v>
+      </c>
+      <c r="I9" s="4">
+        <v>5</v>
+      </c>
+      <c r="J9" s="4">
+        <v>5</v>
+      </c>
+      <c r="K9" s="4">
+        <v>5</v>
+      </c>
+      <c r="L9" s="4">
+        <v>8</v>
+      </c>
+      <c r="M9" s="4">
+        <v>8</v>
+      </c>
+      <c r="N9" s="4">
+        <v>8</v>
+      </c>
+      <c r="O9" s="4">
+        <v>10</v>
+      </c>
+      <c r="P9" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q9" s="4">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="R9" s="4">
+        <f t="shared" si="1"/>
+        <v>91.428571428571431</v>
+      </c>
       <c r="S9" s="4"/>
-    </row>
-    <row r="10" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T9" s="4"/>
+    </row>
+    <row r="10" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>4</v>
       </c>
@@ -5922,22 +6019,51 @@
       <c r="E10" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
+      <c r="F10" s="4">
+        <v>4</v>
+      </c>
+      <c r="G10" s="4">
+        <v>4</v>
+      </c>
+      <c r="H10" s="4">
+        <v>5</v>
+      </c>
+      <c r="I10" s="4">
+        <v>5</v>
+      </c>
+      <c r="J10" s="4">
+        <v>4</v>
+      </c>
+      <c r="K10" s="4">
+        <v>5</v>
+      </c>
+      <c r="L10" s="4">
+        <v>9</v>
+      </c>
+      <c r="M10" s="4">
+        <v>9</v>
+      </c>
+      <c r="N10" s="4">
+        <v>8</v>
+      </c>
+      <c r="O10" s="4">
+        <v>10</v>
+      </c>
+      <c r="P10" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q10" s="4">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="R10" s="4">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
       <c r="S10" s="4"/>
-    </row>
-    <row r="11" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T10" s="4"/>
+    </row>
+    <row r="11" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>5</v>
       </c>
@@ -5953,22 +6079,51 @@
       <c r="E11" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
+      <c r="F11" s="4">
+        <v>5</v>
+      </c>
+      <c r="G11" s="4">
+        <v>5</v>
+      </c>
+      <c r="H11" s="4">
+        <v>5</v>
+      </c>
+      <c r="I11" s="4">
+        <v>4</v>
+      </c>
+      <c r="J11" s="4">
+        <v>4</v>
+      </c>
+      <c r="K11" s="4">
+        <v>5</v>
+      </c>
+      <c r="L11" s="4">
+        <v>9</v>
+      </c>
+      <c r="M11" s="4">
+        <v>9</v>
+      </c>
+      <c r="N11" s="4">
+        <v>7</v>
+      </c>
+      <c r="O11" s="4">
+        <v>10</v>
+      </c>
+      <c r="P11" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q11" s="4">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="R11" s="4">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
       <c r="S11" s="4"/>
-    </row>
-    <row r="12" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T11" s="4"/>
+    </row>
+    <row r="12" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>6</v>
       </c>
@@ -5984,22 +6139,51 @@
       <c r="E12" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
+      <c r="F12" s="4">
+        <v>5</v>
+      </c>
+      <c r="G12" s="4">
+        <v>5</v>
+      </c>
+      <c r="H12" s="4">
+        <v>5</v>
+      </c>
+      <c r="I12" s="4">
+        <v>5</v>
+      </c>
+      <c r="J12" s="4">
+        <v>4</v>
+      </c>
+      <c r="K12" s="4">
+        <v>4</v>
+      </c>
+      <c r="L12" s="4">
+        <v>9</v>
+      </c>
+      <c r="M12" s="4">
+        <v>9</v>
+      </c>
+      <c r="N12" s="4">
+        <v>10</v>
+      </c>
+      <c r="O12" s="4">
+        <v>10</v>
+      </c>
+      <c r="P12" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q12" s="4">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="R12" s="4">
+        <f t="shared" si="1"/>
+        <v>94.285714285714278</v>
+      </c>
       <c r="S12" s="4"/>
-    </row>
-    <row r="13" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T12" s="4"/>
+    </row>
+    <row r="13" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>7</v>
       </c>
@@ -6015,22 +6199,51 @@
       <c r="E13" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
+      <c r="F13" s="4">
+        <v>5</v>
+      </c>
+      <c r="G13" s="4">
+        <v>5</v>
+      </c>
+      <c r="H13" s="4">
+        <v>4</v>
+      </c>
+      <c r="I13" s="4">
+        <v>4</v>
+      </c>
+      <c r="J13" s="4">
+        <v>4</v>
+      </c>
+      <c r="K13" s="4">
+        <v>4</v>
+      </c>
+      <c r="L13" s="4">
+        <v>9</v>
+      </c>
+      <c r="M13" s="4">
+        <v>9</v>
+      </c>
+      <c r="N13" s="4">
+        <v>9</v>
+      </c>
+      <c r="O13" s="4">
+        <v>10</v>
+      </c>
+      <c r="P13" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q13" s="4">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="R13" s="4">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
       <c r="S13" s="4"/>
-    </row>
-    <row r="14" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T13" s="4"/>
+    </row>
+    <row r="14" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>8</v>
       </c>
@@ -6046,22 +6259,51 @@
       <c r="E14" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
+      <c r="F14" s="4">
+        <v>4</v>
+      </c>
+      <c r="G14" s="4">
+        <v>4</v>
+      </c>
+      <c r="H14" s="4">
+        <v>4</v>
+      </c>
+      <c r="I14" s="4">
+        <v>4</v>
+      </c>
+      <c r="J14" s="4">
+        <v>3</v>
+      </c>
+      <c r="K14" s="4">
+        <v>4</v>
+      </c>
+      <c r="L14" s="4">
+        <v>7</v>
+      </c>
+      <c r="M14" s="4">
+        <v>7</v>
+      </c>
+      <c r="N14" s="4">
+        <v>9</v>
+      </c>
+      <c r="O14" s="4">
+        <v>10</v>
+      </c>
+      <c r="P14" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q14" s="4">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="R14" s="4">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
       <c r="S14" s="4"/>
-    </row>
-    <row r="15" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T14" s="4"/>
+    </row>
+    <row r="15" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>9</v>
       </c>
@@ -6077,22 +6319,51 @@
       <c r="E15" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
+      <c r="F15" s="4">
+        <v>5</v>
+      </c>
+      <c r="G15" s="4">
+        <v>5</v>
+      </c>
+      <c r="H15" s="4">
+        <v>5</v>
+      </c>
+      <c r="I15" s="4">
+        <v>5</v>
+      </c>
+      <c r="J15" s="4">
+        <v>4</v>
+      </c>
+      <c r="K15" s="4">
+        <v>5</v>
+      </c>
+      <c r="L15" s="4">
+        <v>8</v>
+      </c>
+      <c r="M15" s="4">
+        <v>9</v>
+      </c>
+      <c r="N15" s="4">
+        <v>7</v>
+      </c>
+      <c r="O15" s="4">
+        <v>10</v>
+      </c>
+      <c r="P15" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q15" s="4">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="R15" s="4">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
       <c r="S15" s="4"/>
-    </row>
-    <row r="16" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T15" s="4"/>
+    </row>
+    <row r="16" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>10</v>
       </c>
@@ -6108,22 +6379,51 @@
       <c r="E16" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="4"/>
+      <c r="F16" s="4">
+        <v>3</v>
+      </c>
+      <c r="G16" s="4">
+        <v>3</v>
+      </c>
+      <c r="H16" s="4">
+        <v>4</v>
+      </c>
+      <c r="I16" s="4">
+        <v>4</v>
+      </c>
+      <c r="J16" s="4">
+        <v>3</v>
+      </c>
+      <c r="K16" s="4">
+        <v>4</v>
+      </c>
+      <c r="L16" s="4">
+        <v>7</v>
+      </c>
+      <c r="M16" s="4">
+        <v>7</v>
+      </c>
+      <c r="N16" s="4">
+        <v>7</v>
+      </c>
+      <c r="O16" s="4">
+        <v>10</v>
+      </c>
+      <c r="P16" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q16" s="4">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="R16" s="4">
+        <f t="shared" si="1"/>
+        <v>74.285714285714292</v>
+      </c>
       <c r="S16" s="4"/>
-    </row>
-    <row r="17" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T16" s="4"/>
+    </row>
+    <row r="17" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>11</v>
       </c>
@@ -6139,22 +6439,51 @@
       <c r="E17" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
+      <c r="F17" s="4">
+        <v>5</v>
+      </c>
+      <c r="G17" s="4">
+        <v>5</v>
+      </c>
+      <c r="H17" s="4">
+        <v>5</v>
+      </c>
+      <c r="I17" s="4">
+        <v>5</v>
+      </c>
+      <c r="J17" s="4">
+        <v>5</v>
+      </c>
+      <c r="K17" s="4">
+        <v>4</v>
+      </c>
+      <c r="L17" s="4">
+        <v>8</v>
+      </c>
+      <c r="M17" s="4">
+        <v>9</v>
+      </c>
+      <c r="N17" s="4">
+        <v>7</v>
+      </c>
+      <c r="O17" s="4">
+        <v>10</v>
+      </c>
+      <c r="P17" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q17" s="4">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="R17" s="4">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
       <c r="S17" s="4"/>
-    </row>
-    <row r="18" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T17" s="4"/>
+    </row>
+    <row r="18" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>12</v>
       </c>
@@ -6170,22 +6499,51 @@
       <c r="E18" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="4"/>
-      <c r="R18" s="4"/>
+      <c r="F18" s="4">
+        <v>5</v>
+      </c>
+      <c r="G18" s="4">
+        <v>4</v>
+      </c>
+      <c r="H18" s="4">
+        <v>4</v>
+      </c>
+      <c r="I18" s="4">
+        <v>4</v>
+      </c>
+      <c r="J18" s="4">
+        <v>3</v>
+      </c>
+      <c r="K18" s="4">
+        <v>4</v>
+      </c>
+      <c r="L18" s="4">
+        <v>8</v>
+      </c>
+      <c r="M18" s="4">
+        <v>8</v>
+      </c>
+      <c r="N18" s="4">
+        <v>7</v>
+      </c>
+      <c r="O18" s="4">
+        <v>10</v>
+      </c>
+      <c r="P18" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q18" s="4">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="R18" s="4">
+        <f t="shared" si="1"/>
+        <v>81.428571428571431</v>
+      </c>
       <c r="S18" s="4"/>
-    </row>
-    <row r="19" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T18" s="4"/>
+    </row>
+    <row r="19" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>13</v>
       </c>
@@ -6201,22 +6559,51 @@
       <c r="E19" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
+      <c r="F19" s="4">
+        <v>5</v>
+      </c>
+      <c r="G19" s="4">
+        <v>5</v>
+      </c>
+      <c r="H19" s="4">
+        <v>5</v>
+      </c>
+      <c r="I19" s="4">
+        <v>5</v>
+      </c>
+      <c r="J19" s="4">
+        <v>4</v>
+      </c>
+      <c r="K19" s="4">
+        <v>4</v>
+      </c>
+      <c r="L19" s="4">
+        <v>8</v>
+      </c>
+      <c r="M19" s="4">
+        <v>9</v>
+      </c>
+      <c r="N19" s="4">
+        <v>8</v>
+      </c>
+      <c r="O19" s="4">
+        <v>10</v>
+      </c>
+      <c r="P19" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q19" s="4">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="R19" s="4">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
       <c r="S19" s="4"/>
-    </row>
-    <row r="20" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T19" s="4"/>
+    </row>
+    <row r="20" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>14</v>
       </c>
@@ -6232,22 +6619,51 @@
       <c r="E20" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="4"/>
+      <c r="F20" s="4">
+        <v>5</v>
+      </c>
+      <c r="G20" s="4">
+        <v>5</v>
+      </c>
+      <c r="H20" s="4">
+        <v>5</v>
+      </c>
+      <c r="I20" s="4">
+        <v>5</v>
+      </c>
+      <c r="J20" s="4">
+        <v>4</v>
+      </c>
+      <c r="K20" s="4">
+        <v>4</v>
+      </c>
+      <c r="L20" s="4">
+        <v>8</v>
+      </c>
+      <c r="M20" s="4">
+        <v>9</v>
+      </c>
+      <c r="N20" s="4">
+        <v>8</v>
+      </c>
+      <c r="O20" s="4">
+        <v>10</v>
+      </c>
+      <c r="P20" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q20" s="4">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="R20" s="4">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
       <c r="S20" s="4"/>
-    </row>
-    <row r="21" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T20" s="4"/>
+    </row>
+    <row r="21" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>15</v>
       </c>
@@ -6263,22 +6679,51 @@
       <c r="E21" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4"/>
+      <c r="F21" s="4">
+        <v>5</v>
+      </c>
+      <c r="G21" s="4">
+        <v>5</v>
+      </c>
+      <c r="H21" s="4">
+        <v>5</v>
+      </c>
+      <c r="I21" s="4">
+        <v>5</v>
+      </c>
+      <c r="J21" s="4">
+        <v>4</v>
+      </c>
+      <c r="K21" s="4">
+        <v>4</v>
+      </c>
+      <c r="L21" s="4">
+        <v>8</v>
+      </c>
+      <c r="M21" s="4">
+        <v>9</v>
+      </c>
+      <c r="N21" s="4">
+        <v>8</v>
+      </c>
+      <c r="O21" s="4">
+        <v>10</v>
+      </c>
+      <c r="P21" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q21" s="4">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="R21" s="4">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
       <c r="S21" s="4"/>
-    </row>
-    <row r="22" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T21" s="4"/>
+    </row>
+    <row r="22" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>16</v>
       </c>
@@ -6294,22 +6739,51 @@
       <c r="E22" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="4"/>
+      <c r="F22" s="4">
+        <v>5</v>
+      </c>
+      <c r="G22" s="4">
+        <v>5</v>
+      </c>
+      <c r="H22" s="4">
+        <v>5</v>
+      </c>
+      <c r="I22" s="4">
+        <v>5</v>
+      </c>
+      <c r="J22" s="4">
+        <v>5</v>
+      </c>
+      <c r="K22" s="4">
+        <v>5</v>
+      </c>
+      <c r="L22" s="4">
+        <v>9</v>
+      </c>
+      <c r="M22" s="4">
+        <v>9</v>
+      </c>
+      <c r="N22" s="4">
+        <v>9</v>
+      </c>
+      <c r="O22" s="4">
+        <v>10</v>
+      </c>
+      <c r="P22" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q22" s="4">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+      <c r="R22" s="4">
+        <f t="shared" si="1"/>
+        <v>95.714285714285722</v>
+      </c>
       <c r="S22" s="4"/>
-    </row>
-    <row r="23" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T22" s="4"/>
+    </row>
+    <row r="23" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>17</v>
       </c>
@@ -6325,22 +6799,51 @@
       <c r="E23" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4"/>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="4"/>
+      <c r="F23" s="4">
+        <v>5</v>
+      </c>
+      <c r="G23" s="4">
+        <v>4</v>
+      </c>
+      <c r="H23" s="4">
+        <v>4</v>
+      </c>
+      <c r="I23" s="4">
+        <v>4</v>
+      </c>
+      <c r="J23" s="4">
+        <v>4</v>
+      </c>
+      <c r="K23" s="4">
+        <v>4</v>
+      </c>
+      <c r="L23" s="4">
+        <v>8</v>
+      </c>
+      <c r="M23" s="4">
+        <v>8</v>
+      </c>
+      <c r="N23" s="4">
+        <v>9</v>
+      </c>
+      <c r="O23" s="4">
+        <v>10</v>
+      </c>
+      <c r="P23" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q23" s="4">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="R23" s="4">
+        <f t="shared" si="1"/>
+        <v>85.714285714285708</v>
+      </c>
       <c r="S23" s="4"/>
-    </row>
-    <row r="24" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T23" s="4"/>
+    </row>
+    <row r="24" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>18</v>
       </c>
@@ -6356,22 +6859,51 @@
       <c r="E24" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="4"/>
-      <c r="R24" s="4"/>
+      <c r="F24" s="4">
+        <v>5</v>
+      </c>
+      <c r="G24" s="4">
+        <v>5</v>
+      </c>
+      <c r="H24" s="4">
+        <v>4</v>
+      </c>
+      <c r="I24" s="4">
+        <v>5</v>
+      </c>
+      <c r="J24" s="4">
+        <v>4</v>
+      </c>
+      <c r="K24" s="4">
+        <v>5</v>
+      </c>
+      <c r="L24" s="4">
+        <v>9</v>
+      </c>
+      <c r="M24" s="4">
+        <v>9</v>
+      </c>
+      <c r="N24" s="4">
+        <v>7</v>
+      </c>
+      <c r="O24" s="4">
+        <v>10</v>
+      </c>
+      <c r="P24" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q24" s="4">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="R24" s="4">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
       <c r="S24" s="4"/>
-    </row>
-    <row r="25" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T24" s="4"/>
+    </row>
+    <row r="25" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>19</v>
       </c>
@@ -6387,22 +6919,51 @@
       <c r="E25" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="4"/>
-      <c r="Q25" s="4"/>
-      <c r="R25" s="4"/>
+      <c r="F25" s="4">
+        <v>5</v>
+      </c>
+      <c r="G25" s="4">
+        <v>5</v>
+      </c>
+      <c r="H25" s="4">
+        <v>4</v>
+      </c>
+      <c r="I25" s="4">
+        <v>5</v>
+      </c>
+      <c r="J25" s="4">
+        <v>4</v>
+      </c>
+      <c r="K25" s="4">
+        <v>5</v>
+      </c>
+      <c r="L25" s="4">
+        <v>9</v>
+      </c>
+      <c r="M25" s="4">
+        <v>9</v>
+      </c>
+      <c r="N25" s="4">
+        <v>7</v>
+      </c>
+      <c r="O25" s="4">
+        <v>10</v>
+      </c>
+      <c r="P25" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q25" s="4">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="R25" s="4">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
       <c r="S25" s="4"/>
-    </row>
-    <row r="26" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T25" s="4"/>
+    </row>
+    <row r="26" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>20</v>
       </c>
@@ -6418,22 +6979,51 @@
       <c r="E26" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="4"/>
-      <c r="Q26" s="4"/>
-      <c r="R26" s="4"/>
+      <c r="F26" s="4">
+        <v>5</v>
+      </c>
+      <c r="G26" s="4">
+        <v>5</v>
+      </c>
+      <c r="H26" s="4">
+        <v>4</v>
+      </c>
+      <c r="I26" s="4">
+        <v>5</v>
+      </c>
+      <c r="J26" s="4">
+        <v>4</v>
+      </c>
+      <c r="K26" s="4">
+        <v>5</v>
+      </c>
+      <c r="L26" s="4">
+        <v>9</v>
+      </c>
+      <c r="M26" s="4">
+        <v>9</v>
+      </c>
+      <c r="N26" s="4">
+        <v>7</v>
+      </c>
+      <c r="O26" s="4">
+        <v>10</v>
+      </c>
+      <c r="P26" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q26" s="4">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="R26" s="4">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
       <c r="S26" s="4"/>
-    </row>
-    <row r="27" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T26" s="4"/>
+    </row>
+    <row r="27" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>21</v>
       </c>
@@ -6449,22 +7039,51 @@
       <c r="E27" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="4"/>
-      <c r="Q27" s="4"/>
-      <c r="R27" s="4"/>
+      <c r="F27" s="4">
+        <v>5</v>
+      </c>
+      <c r="G27" s="4">
+        <v>5</v>
+      </c>
+      <c r="H27" s="4">
+        <v>4</v>
+      </c>
+      <c r="I27" s="4">
+        <v>5</v>
+      </c>
+      <c r="J27" s="4">
+        <v>4</v>
+      </c>
+      <c r="K27" s="4">
+        <v>5</v>
+      </c>
+      <c r="L27" s="4">
+        <v>9</v>
+      </c>
+      <c r="M27" s="4">
+        <v>9</v>
+      </c>
+      <c r="N27" s="4">
+        <v>7</v>
+      </c>
+      <c r="O27" s="4">
+        <v>10</v>
+      </c>
+      <c r="P27" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q27" s="4">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="R27" s="4">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
       <c r="S27" s="4"/>
-    </row>
-    <row r="28" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T27" s="4"/>
+    </row>
+    <row r="28" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>22</v>
       </c>
@@ -6480,22 +7099,51 @@
       <c r="E28" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="4"/>
-      <c r="Q28" s="4"/>
-      <c r="R28" s="4"/>
+      <c r="F28" s="4">
+        <v>5</v>
+      </c>
+      <c r="G28" s="4">
+        <v>5</v>
+      </c>
+      <c r="H28" s="4">
+        <v>4</v>
+      </c>
+      <c r="I28" s="4">
+        <v>5</v>
+      </c>
+      <c r="J28" s="4">
+        <v>4</v>
+      </c>
+      <c r="K28" s="4">
+        <v>5</v>
+      </c>
+      <c r="L28" s="4">
+        <v>9</v>
+      </c>
+      <c r="M28" s="4">
+        <v>9</v>
+      </c>
+      <c r="N28" s="4">
+        <v>7</v>
+      </c>
+      <c r="O28" s="4">
+        <v>10</v>
+      </c>
+      <c r="P28" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q28" s="4">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="R28" s="4">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
       <c r="S28" s="4"/>
-    </row>
-    <row r="29" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T28" s="4"/>
+    </row>
+    <row r="29" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>23</v>
       </c>
@@ -6511,22 +7159,51 @@
       <c r="E29" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="4"/>
-      <c r="Q29" s="4"/>
-      <c r="R29" s="4"/>
+      <c r="F29" s="4">
+        <v>5</v>
+      </c>
+      <c r="G29" s="4">
+        <v>5</v>
+      </c>
+      <c r="H29" s="4">
+        <v>4</v>
+      </c>
+      <c r="I29" s="4">
+        <v>5</v>
+      </c>
+      <c r="J29" s="4">
+        <v>4</v>
+      </c>
+      <c r="K29" s="4">
+        <v>5</v>
+      </c>
+      <c r="L29" s="4">
+        <v>9</v>
+      </c>
+      <c r="M29" s="4">
+        <v>9</v>
+      </c>
+      <c r="N29" s="4">
+        <v>7</v>
+      </c>
+      <c r="O29" s="4">
+        <v>10</v>
+      </c>
+      <c r="P29" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q29" s="4">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="R29" s="4">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
       <c r="S29" s="4"/>
-    </row>
-    <row r="30" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T29" s="4"/>
+    </row>
+    <row r="30" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>24</v>
       </c>
@@ -6542,22 +7219,51 @@
       <c r="E30" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="4"/>
+      <c r="F30" s="4">
+        <v>5</v>
+      </c>
+      <c r="G30" s="4">
+        <v>5</v>
+      </c>
+      <c r="H30" s="4">
+        <v>4</v>
+      </c>
+      <c r="I30" s="4">
+        <v>5</v>
+      </c>
+      <c r="J30" s="4">
+        <v>4</v>
+      </c>
+      <c r="K30" s="4">
+        <v>5</v>
+      </c>
+      <c r="L30" s="4">
+        <v>9</v>
+      </c>
+      <c r="M30" s="4">
+        <v>9</v>
+      </c>
+      <c r="N30" s="4">
+        <v>7</v>
+      </c>
+      <c r="O30" s="4">
+        <v>10</v>
+      </c>
+      <c r="P30" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q30" s="4">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="R30" s="4">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
       <c r="S30" s="4"/>
-    </row>
-    <row r="31" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T30" s="4"/>
+    </row>
+    <row r="31" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>25</v>
       </c>
@@ -6569,45 +7275,75 @@
       <c r="E31" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
-      <c r="Q31" s="4"/>
-      <c r="R31" s="4"/>
+      <c r="F31" s="4">
+        <v>5</v>
+      </c>
+      <c r="G31" s="4">
+        <v>5</v>
+      </c>
+      <c r="H31" s="4">
+        <v>4</v>
+      </c>
+      <c r="I31" s="4">
+        <v>5</v>
+      </c>
+      <c r="J31" s="4">
+        <v>4</v>
+      </c>
+      <c r="K31" s="4">
+        <v>5</v>
+      </c>
+      <c r="L31" s="4">
+        <v>9</v>
+      </c>
+      <c r="M31" s="4">
+        <v>9</v>
+      </c>
+      <c r="N31" s="4">
+        <v>7</v>
+      </c>
+      <c r="O31" s="4">
+        <v>7</v>
+      </c>
+      <c r="P31" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q31" s="4">
+        <f>SUM(F31:O31)</f>
+        <v>60</v>
+      </c>
+      <c r="R31" s="4">
+        <f t="shared" si="1"/>
+        <v>85.714285714285708</v>
+      </c>
       <c r="S31" s="4"/>
-    </row>
-    <row r="32" spans="1:19" ht="21" x14ac:dyDescent="0.2">
-      <c r="A32" s="40" t="s">
+      <c r="T31" s="4"/>
+    </row>
+    <row r="32" spans="1:20" ht="21" x14ac:dyDescent="0.2">
+      <c r="A32" s="42" t="s">
         <v>225</v>
       </c>
-      <c r="B32" s="41"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="41"/>
-      <c r="I32" s="41"/>
-      <c r="J32" s="41"/>
-      <c r="K32" s="41"/>
-      <c r="L32" s="41"/>
-      <c r="M32" s="41"/>
-      <c r="N32" s="41"/>
-      <c r="O32" s="41"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="41"/>
-      <c r="S32" s="42"/>
-    </row>
-    <row r="33" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="B32" s="43"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="43"/>
+      <c r="L32" s="43"/>
+      <c r="M32" s="43"/>
+      <c r="N32" s="43"/>
+      <c r="O32" s="43"/>
+      <c r="P32" s="43"/>
+      <c r="Q32" s="43"/>
+      <c r="R32" s="43"/>
+      <c r="S32" s="43"/>
+      <c r="T32" s="44"/>
+    </row>
+    <row r="33" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A33" s="11">
         <v>26</v>
       </c>
@@ -6623,22 +7359,51 @@
       <c r="E33" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4"/>
-      <c r="R33" s="4"/>
+      <c r="F33" s="4">
+        <v>5</v>
+      </c>
+      <c r="G33" s="4">
+        <v>4</v>
+      </c>
+      <c r="H33" s="4">
+        <v>4</v>
+      </c>
+      <c r="I33" s="4">
+        <v>5</v>
+      </c>
+      <c r="J33" s="4">
+        <v>5</v>
+      </c>
+      <c r="K33" s="4">
+        <v>5</v>
+      </c>
+      <c r="L33" s="4">
+        <v>8</v>
+      </c>
+      <c r="M33" s="4">
+        <v>8</v>
+      </c>
+      <c r="N33" s="4">
+        <v>9</v>
+      </c>
+      <c r="O33" s="4">
+        <v>10</v>
+      </c>
+      <c r="P33" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q33" s="4">
+        <f>SUM(F33:O33)</f>
+        <v>63</v>
+      </c>
+      <c r="R33" s="4">
+        <f>Q33/P33*100</f>
+        <v>90</v>
+      </c>
       <c r="S33" s="4"/>
-    </row>
-    <row r="34" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T33" s="4"/>
+    </row>
+    <row r="34" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A34" s="9">
         <v>27</v>
       </c>
@@ -6654,22 +7419,51 @@
       <c r="E34" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4"/>
-      <c r="R34" s="4"/>
+      <c r="F34" s="4">
+        <v>4</v>
+      </c>
+      <c r="G34" s="4">
+        <v>4</v>
+      </c>
+      <c r="H34" s="4">
+        <v>4</v>
+      </c>
+      <c r="I34" s="4">
+        <v>4</v>
+      </c>
+      <c r="J34" s="4">
+        <v>4</v>
+      </c>
+      <c r="K34" s="4">
+        <v>4</v>
+      </c>
+      <c r="L34" s="4">
+        <v>9</v>
+      </c>
+      <c r="M34" s="4">
+        <v>9</v>
+      </c>
+      <c r="N34" s="4">
+        <v>9</v>
+      </c>
+      <c r="O34" s="4">
+        <v>10</v>
+      </c>
+      <c r="P34" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q34" s="4">
+        <f t="shared" ref="Q34:Q63" si="2">SUM(F34:O34)</f>
+        <v>61</v>
+      </c>
+      <c r="R34" s="4">
+        <f t="shared" ref="R34:R63" si="3">Q34/P34*100</f>
+        <v>87.142857142857139</v>
+      </c>
       <c r="S34" s="4"/>
-    </row>
-    <row r="35" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T34" s="4"/>
+    </row>
+    <row r="35" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A35" s="11">
         <v>28</v>
       </c>
@@ -6685,22 +7479,51 @@
       <c r="E35" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="4"/>
+      <c r="F35" s="4">
+        <v>5</v>
+      </c>
+      <c r="G35" s="4">
+        <v>5</v>
+      </c>
+      <c r="H35" s="4">
+        <v>3</v>
+      </c>
+      <c r="I35" s="4">
+        <v>4</v>
+      </c>
+      <c r="J35" s="4">
+        <v>3</v>
+      </c>
+      <c r="K35" s="4">
+        <v>4</v>
+      </c>
+      <c r="L35" s="4">
+        <v>8</v>
+      </c>
+      <c r="M35" s="4">
+        <v>8</v>
+      </c>
+      <c r="N35" s="4">
+        <v>8</v>
+      </c>
+      <c r="O35" s="4">
+        <v>10</v>
+      </c>
+      <c r="P35" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q35" s="4">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+      <c r="R35" s="4">
+        <f t="shared" si="3"/>
+        <v>82.857142857142861</v>
+      </c>
       <c r="S35" s="4"/>
-    </row>
-    <row r="36" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T35" s="4"/>
+    </row>
+    <row r="36" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A36" s="9">
         <v>29</v>
       </c>
@@ -6716,22 +7539,51 @@
       <c r="E36" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
+      <c r="F36" s="4">
+        <v>5</v>
+      </c>
+      <c r="G36" s="4">
+        <v>4</v>
+      </c>
+      <c r="H36" s="4">
+        <v>3</v>
+      </c>
+      <c r="I36" s="4">
+        <v>4</v>
+      </c>
+      <c r="J36" s="4">
+        <v>3</v>
+      </c>
+      <c r="K36" s="4">
+        <v>4</v>
+      </c>
+      <c r="L36" s="4">
+        <v>7</v>
+      </c>
+      <c r="M36" s="4">
+        <v>7</v>
+      </c>
+      <c r="N36" s="4">
+        <v>8</v>
+      </c>
+      <c r="O36" s="4">
+        <v>6</v>
+      </c>
+      <c r="P36" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q36" s="4">
+        <f t="shared" si="2"/>
+        <v>51</v>
+      </c>
+      <c r="R36" s="4">
+        <f t="shared" si="3"/>
+        <v>72.857142857142847</v>
+      </c>
       <c r="S36" s="4"/>
-    </row>
-    <row r="37" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T36" s="4"/>
+    </row>
+    <row r="37" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A37" s="11">
         <v>30</v>
       </c>
@@ -6747,22 +7599,51 @@
       <c r="E37" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
-      <c r="Q37" s="4"/>
-      <c r="R37" s="4"/>
+      <c r="F37" s="4">
+        <v>3</v>
+      </c>
+      <c r="G37" s="4">
+        <v>4</v>
+      </c>
+      <c r="H37" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="I37" s="4">
+        <v>3</v>
+      </c>
+      <c r="J37" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="K37" s="4">
+        <v>4</v>
+      </c>
+      <c r="L37" s="4">
+        <v>8</v>
+      </c>
+      <c r="M37" s="4">
+        <v>8</v>
+      </c>
+      <c r="N37" s="4">
+        <v>8</v>
+      </c>
+      <c r="O37" s="4">
+        <v>8</v>
+      </c>
+      <c r="P37" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q37" s="4">
+        <f t="shared" si="2"/>
+        <v>51</v>
+      </c>
+      <c r="R37" s="4">
+        <f t="shared" si="3"/>
+        <v>72.857142857142847</v>
+      </c>
       <c r="S37" s="4"/>
-    </row>
-    <row r="38" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T37" s="4"/>
+    </row>
+    <row r="38" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A38" s="9">
         <v>31</v>
       </c>
@@ -6778,22 +7659,51 @@
       <c r="E38" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="4"/>
-      <c r="Q38" s="4"/>
-      <c r="R38" s="4"/>
+      <c r="F38" s="4">
+        <v>4</v>
+      </c>
+      <c r="G38" s="4">
+        <v>4</v>
+      </c>
+      <c r="H38" s="4">
+        <v>3</v>
+      </c>
+      <c r="I38" s="4">
+        <v>3</v>
+      </c>
+      <c r="J38" s="4">
+        <v>3</v>
+      </c>
+      <c r="K38" s="4">
+        <v>4</v>
+      </c>
+      <c r="L38" s="4">
+        <v>8</v>
+      </c>
+      <c r="M38" s="4">
+        <v>8</v>
+      </c>
+      <c r="N38" s="4">
+        <v>7</v>
+      </c>
+      <c r="O38" s="4">
+        <v>10</v>
+      </c>
+      <c r="P38" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q38" s="4">
+        <f t="shared" si="2"/>
+        <v>54</v>
+      </c>
+      <c r="R38" s="4">
+        <f t="shared" si="3"/>
+        <v>77.142857142857153</v>
+      </c>
       <c r="S38" s="4"/>
-    </row>
-    <row r="39" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T38" s="4"/>
+    </row>
+    <row r="39" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A39" s="11">
         <v>32</v>
       </c>
@@ -6809,22 +7719,51 @@
       <c r="E39" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
-      <c r="N39" s="4"/>
-      <c r="O39" s="4"/>
-      <c r="P39" s="4"/>
-      <c r="Q39" s="4"/>
-      <c r="R39" s="4"/>
+      <c r="F39" s="4">
+        <v>5</v>
+      </c>
+      <c r="G39" s="4">
+        <v>5</v>
+      </c>
+      <c r="H39" s="4">
+        <v>2</v>
+      </c>
+      <c r="I39" s="4">
+        <v>3</v>
+      </c>
+      <c r="J39" s="4">
+        <v>2</v>
+      </c>
+      <c r="K39" s="4">
+        <v>4</v>
+      </c>
+      <c r="L39" s="4">
+        <v>8</v>
+      </c>
+      <c r="M39" s="4">
+        <v>8</v>
+      </c>
+      <c r="N39" s="4">
+        <v>8</v>
+      </c>
+      <c r="O39" s="4">
+        <v>10</v>
+      </c>
+      <c r="P39" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q39" s="4">
+        <f t="shared" si="2"/>
+        <v>55</v>
+      </c>
+      <c r="R39" s="4">
+        <f t="shared" si="3"/>
+        <v>78.571428571428569</v>
+      </c>
       <c r="S39" s="4"/>
-    </row>
-    <row r="40" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T39" s="4"/>
+    </row>
+    <row r="40" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A40" s="9">
         <v>33</v>
       </c>
@@ -6840,22 +7779,51 @@
       <c r="E40" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="4"/>
-      <c r="P40" s="4"/>
-      <c r="Q40" s="4"/>
-      <c r="R40" s="4"/>
+      <c r="F40" s="4">
+        <v>5</v>
+      </c>
+      <c r="G40" s="4">
+        <v>5</v>
+      </c>
+      <c r="H40" s="4">
+        <v>5</v>
+      </c>
+      <c r="I40" s="4">
+        <v>5</v>
+      </c>
+      <c r="J40" s="4">
+        <v>5</v>
+      </c>
+      <c r="K40" s="4">
+        <v>4</v>
+      </c>
+      <c r="L40" s="4">
+        <v>8</v>
+      </c>
+      <c r="M40" s="4">
+        <v>8</v>
+      </c>
+      <c r="N40" s="4">
+        <v>8</v>
+      </c>
+      <c r="O40" s="4">
+        <v>10</v>
+      </c>
+      <c r="P40" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q40" s="4">
+        <f t="shared" si="2"/>
+        <v>63</v>
+      </c>
+      <c r="R40" s="4">
+        <f t="shared" si="3"/>
+        <v>90</v>
+      </c>
       <c r="S40" s="4"/>
-    </row>
-    <row r="41" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T40" s="4"/>
+    </row>
+    <row r="41" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A41" s="11">
         <v>34</v>
       </c>
@@ -6871,22 +7839,51 @@
       <c r="E41" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4"/>
-      <c r="P41" s="4"/>
-      <c r="Q41" s="4"/>
-      <c r="R41" s="4"/>
+      <c r="F41" s="4">
+        <v>5</v>
+      </c>
+      <c r="G41" s="4">
+        <v>5</v>
+      </c>
+      <c r="H41" s="4">
+        <v>4</v>
+      </c>
+      <c r="I41" s="4">
+        <v>5</v>
+      </c>
+      <c r="J41" s="4">
+        <v>4</v>
+      </c>
+      <c r="K41" s="4">
+        <v>5</v>
+      </c>
+      <c r="L41" s="4">
+        <v>9</v>
+      </c>
+      <c r="M41" s="4">
+        <v>9</v>
+      </c>
+      <c r="N41" s="4">
+        <v>7</v>
+      </c>
+      <c r="O41" s="4">
+        <v>10</v>
+      </c>
+      <c r="P41" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q41" s="4">
+        <f t="shared" si="2"/>
+        <v>63</v>
+      </c>
+      <c r="R41" s="4">
+        <f t="shared" si="3"/>
+        <v>90</v>
+      </c>
       <c r="S41" s="4"/>
-    </row>
-    <row r="42" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T41" s="4"/>
+    </row>
+    <row r="42" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A42" s="9">
         <v>35</v>
       </c>
@@ -6902,22 +7899,51 @@
       <c r="E42" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4"/>
-      <c r="P42" s="4"/>
-      <c r="Q42" s="4"/>
-      <c r="R42" s="4"/>
+      <c r="F42" s="4">
+        <v>5</v>
+      </c>
+      <c r="G42" s="4">
+        <v>5</v>
+      </c>
+      <c r="H42" s="4">
+        <v>4</v>
+      </c>
+      <c r="I42" s="4">
+        <v>4</v>
+      </c>
+      <c r="J42" s="4">
+        <v>5</v>
+      </c>
+      <c r="K42" s="4">
+        <v>5</v>
+      </c>
+      <c r="L42" s="4">
+        <v>8</v>
+      </c>
+      <c r="M42" s="4">
+        <v>9</v>
+      </c>
+      <c r="N42" s="4">
+        <v>8</v>
+      </c>
+      <c r="O42" s="4">
+        <v>10</v>
+      </c>
+      <c r="P42" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q42" s="4">
+        <f t="shared" si="2"/>
+        <v>63</v>
+      </c>
+      <c r="R42" s="4">
+        <f t="shared" si="3"/>
+        <v>90</v>
+      </c>
       <c r="S42" s="4"/>
-    </row>
-    <row r="43" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T42" s="4"/>
+    </row>
+    <row r="43" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A43" s="11">
         <v>36</v>
       </c>
@@ -6933,22 +7959,51 @@
       <c r="E43" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="4"/>
-      <c r="M43" s="4"/>
-      <c r="N43" s="4"/>
-      <c r="O43" s="4"/>
-      <c r="P43" s="4"/>
-      <c r="Q43" s="4"/>
-      <c r="R43" s="4"/>
+      <c r="F43" s="4">
+        <v>5</v>
+      </c>
+      <c r="G43" s="4">
+        <v>5</v>
+      </c>
+      <c r="H43" s="4">
+        <v>4</v>
+      </c>
+      <c r="I43" s="4">
+        <v>5</v>
+      </c>
+      <c r="J43" s="4">
+        <v>4</v>
+      </c>
+      <c r="K43" s="4">
+        <v>4</v>
+      </c>
+      <c r="L43" s="4">
+        <v>8</v>
+      </c>
+      <c r="M43" s="4">
+        <v>9</v>
+      </c>
+      <c r="N43" s="4">
+        <v>7</v>
+      </c>
+      <c r="O43" s="4">
+        <v>10</v>
+      </c>
+      <c r="P43" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q43" s="4">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="R43" s="4">
+        <f t="shared" si="3"/>
+        <v>87.142857142857139</v>
+      </c>
       <c r="S43" s="4"/>
-    </row>
-    <row r="44" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T43" s="4"/>
+    </row>
+    <row r="44" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A44" s="9">
         <v>37</v>
       </c>
@@ -6964,22 +8019,51 @@
       <c r="E44" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
-      <c r="M44" s="4"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4"/>
-      <c r="P44" s="4"/>
-      <c r="Q44" s="4"/>
-      <c r="R44" s="4"/>
+      <c r="F44" s="4">
+        <v>5</v>
+      </c>
+      <c r="G44" s="4">
+        <v>5</v>
+      </c>
+      <c r="H44" s="4">
+        <v>4</v>
+      </c>
+      <c r="I44" s="4">
+        <v>5</v>
+      </c>
+      <c r="J44" s="4">
+        <v>4</v>
+      </c>
+      <c r="K44" s="4">
+        <v>4</v>
+      </c>
+      <c r="L44" s="4">
+        <v>9</v>
+      </c>
+      <c r="M44" s="4">
+        <v>8</v>
+      </c>
+      <c r="N44" s="4">
+        <v>9</v>
+      </c>
+      <c r="O44" s="4">
+        <v>8</v>
+      </c>
+      <c r="P44" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q44" s="4">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="R44" s="4">
+        <f t="shared" si="3"/>
+        <v>87.142857142857139</v>
+      </c>
       <c r="S44" s="4"/>
-    </row>
-    <row r="45" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T44" s="4"/>
+    </row>
+    <row r="45" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A45" s="11">
         <v>38</v>
       </c>
@@ -6995,22 +8079,51 @@
       <c r="E45" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="4"/>
-      <c r="L45" s="4"/>
-      <c r="M45" s="4"/>
-      <c r="N45" s="4"/>
-      <c r="O45" s="4"/>
-      <c r="P45" s="4"/>
-      <c r="Q45" s="4"/>
-      <c r="R45" s="4"/>
+      <c r="F45" s="4">
+        <v>5</v>
+      </c>
+      <c r="G45" s="4">
+        <v>5</v>
+      </c>
+      <c r="H45" s="4">
+        <v>4</v>
+      </c>
+      <c r="I45" s="4">
+        <v>5</v>
+      </c>
+      <c r="J45" s="4">
+        <v>4</v>
+      </c>
+      <c r="K45" s="4">
+        <v>5</v>
+      </c>
+      <c r="L45" s="4">
+        <v>9</v>
+      </c>
+      <c r="M45" s="4">
+        <v>8</v>
+      </c>
+      <c r="N45" s="4">
+        <v>9</v>
+      </c>
+      <c r="O45" s="4">
+        <v>9</v>
+      </c>
+      <c r="P45" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q45" s="4">
+        <f t="shared" si="2"/>
+        <v>63</v>
+      </c>
+      <c r="R45" s="4">
+        <f t="shared" si="3"/>
+        <v>90</v>
+      </c>
       <c r="S45" s="4"/>
-    </row>
-    <row r="46" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T45" s="4"/>
+    </row>
+    <row r="46" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A46" s="9">
         <v>39</v>
       </c>
@@ -7026,22 +8139,51 @@
       <c r="E46" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="4"/>
-      <c r="L46" s="4"/>
-      <c r="M46" s="4"/>
-      <c r="N46" s="4"/>
-      <c r="O46" s="4"/>
-      <c r="P46" s="4"/>
-      <c r="Q46" s="4"/>
-      <c r="R46" s="4"/>
+      <c r="F46" s="4">
+        <v>4</v>
+      </c>
+      <c r="G46" s="4">
+        <v>4</v>
+      </c>
+      <c r="H46" s="4">
+        <v>4</v>
+      </c>
+      <c r="I46" s="4">
+        <v>5</v>
+      </c>
+      <c r="J46" s="4">
+        <v>4</v>
+      </c>
+      <c r="K46" s="4">
+        <v>4</v>
+      </c>
+      <c r="L46" s="4">
+        <v>8</v>
+      </c>
+      <c r="M46" s="4">
+        <v>8</v>
+      </c>
+      <c r="N46" s="4">
+        <v>8</v>
+      </c>
+      <c r="O46" s="4">
+        <v>9</v>
+      </c>
+      <c r="P46" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q46" s="4">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+      <c r="R46" s="4">
+        <f t="shared" si="3"/>
+        <v>82.857142857142861</v>
+      </c>
       <c r="S46" s="4"/>
-    </row>
-    <row r="47" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T46" s="4"/>
+    </row>
+    <row r="47" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A47" s="11">
         <v>40</v>
       </c>
@@ -7057,22 +8199,51 @@
       <c r="E47" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
-      <c r="M47" s="4"/>
-      <c r="N47" s="4"/>
-      <c r="O47" s="4"/>
-      <c r="P47" s="4"/>
-      <c r="Q47" s="4"/>
-      <c r="R47" s="4"/>
+      <c r="F47" s="4">
+        <v>4</v>
+      </c>
+      <c r="G47" s="4">
+        <v>4</v>
+      </c>
+      <c r="H47" s="4">
+        <v>3</v>
+      </c>
+      <c r="I47" s="4">
+        <v>3</v>
+      </c>
+      <c r="J47" s="4">
+        <v>3</v>
+      </c>
+      <c r="K47" s="4">
+        <v>4</v>
+      </c>
+      <c r="L47" s="4">
+        <v>8</v>
+      </c>
+      <c r="M47" s="4">
+        <v>7</v>
+      </c>
+      <c r="N47" s="4">
+        <v>6</v>
+      </c>
+      <c r="O47" s="4">
+        <v>8</v>
+      </c>
+      <c r="P47" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q47" s="4">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="R47" s="4">
+        <f t="shared" si="3"/>
+        <v>71.428571428571431</v>
+      </c>
       <c r="S47" s="4"/>
-    </row>
-    <row r="48" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T47" s="4"/>
+    </row>
+    <row r="48" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A48" s="9">
         <v>41</v>
       </c>
@@ -7088,22 +8259,51 @@
       <c r="E48" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
-      <c r="N48" s="4"/>
-      <c r="O48" s="4"/>
-      <c r="P48" s="4"/>
-      <c r="Q48" s="4"/>
-      <c r="R48" s="4"/>
+      <c r="F48" s="4">
+        <v>4</v>
+      </c>
+      <c r="G48" s="4">
+        <v>4</v>
+      </c>
+      <c r="H48" s="4">
+        <v>3</v>
+      </c>
+      <c r="I48" s="4">
+        <v>3</v>
+      </c>
+      <c r="J48" s="4">
+        <v>3</v>
+      </c>
+      <c r="K48" s="4">
+        <v>3</v>
+      </c>
+      <c r="L48" s="4">
+        <v>7</v>
+      </c>
+      <c r="M48" s="4">
+        <v>7</v>
+      </c>
+      <c r="N48" s="4">
+        <v>8</v>
+      </c>
+      <c r="O48" s="4">
+        <v>7</v>
+      </c>
+      <c r="P48" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q48" s="4">
+        <f t="shared" si="2"/>
+        <v>49</v>
+      </c>
+      <c r="R48" s="4">
+        <f t="shared" si="3"/>
+        <v>70</v>
+      </c>
       <c r="S48" s="4"/>
-    </row>
-    <row r="49" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T48" s="4"/>
+    </row>
+    <row r="49" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A49" s="11">
         <v>42</v>
       </c>
@@ -7119,22 +8319,51 @@
       <c r="E49" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
-      <c r="M49" s="4"/>
-      <c r="N49" s="4"/>
-      <c r="O49" s="4"/>
-      <c r="P49" s="4"/>
-      <c r="Q49" s="4"/>
-      <c r="R49" s="4"/>
+      <c r="F49" s="4">
+        <v>4</v>
+      </c>
+      <c r="G49" s="4">
+        <v>4</v>
+      </c>
+      <c r="H49" s="4">
+        <v>5</v>
+      </c>
+      <c r="I49" s="4">
+        <v>5</v>
+      </c>
+      <c r="J49" s="4">
+        <v>4</v>
+      </c>
+      <c r="K49" s="4">
+        <v>4</v>
+      </c>
+      <c r="L49" s="4">
+        <v>8</v>
+      </c>
+      <c r="M49" s="4">
+        <v>9</v>
+      </c>
+      <c r="N49" s="4">
+        <v>9</v>
+      </c>
+      <c r="O49" s="4">
+        <v>10</v>
+      </c>
+      <c r="P49" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q49" s="4">
+        <f t="shared" si="2"/>
+        <v>62</v>
+      </c>
+      <c r="R49" s="4">
+        <f t="shared" si="3"/>
+        <v>88.571428571428569</v>
+      </c>
       <c r="S49" s="4"/>
-    </row>
-    <row r="50" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T49" s="4"/>
+    </row>
+    <row r="50" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A50" s="9">
         <v>43</v>
       </c>
@@ -7150,22 +8379,51 @@
       <c r="E50" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4"/>
-      <c r="N50" s="4"/>
-      <c r="O50" s="4"/>
-      <c r="P50" s="4"/>
-      <c r="Q50" s="4"/>
-      <c r="R50" s="4"/>
+      <c r="F50" s="4">
+        <v>4</v>
+      </c>
+      <c r="G50" s="4">
+        <v>4</v>
+      </c>
+      <c r="H50" s="4">
+        <v>4</v>
+      </c>
+      <c r="I50" s="4">
+        <v>4</v>
+      </c>
+      <c r="J50" s="4">
+        <v>3</v>
+      </c>
+      <c r="K50" s="4">
+        <v>4</v>
+      </c>
+      <c r="L50" s="4">
+        <v>8</v>
+      </c>
+      <c r="M50" s="4">
+        <v>9</v>
+      </c>
+      <c r="N50" s="4">
+        <v>7</v>
+      </c>
+      <c r="O50" s="4">
+        <v>10</v>
+      </c>
+      <c r="P50" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q50" s="4">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="R50" s="4">
+        <f t="shared" si="3"/>
+        <v>81.428571428571431</v>
+      </c>
       <c r="S50" s="4"/>
-    </row>
-    <row r="51" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T50" s="4"/>
+    </row>
+    <row r="51" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A51" s="11">
         <v>44</v>
       </c>
@@ -7181,22 +8439,51 @@
       <c r="E51" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
-      <c r="Q51" s="4"/>
-      <c r="R51" s="4"/>
+      <c r="F51" s="4">
+        <v>4</v>
+      </c>
+      <c r="G51" s="4">
+        <v>4</v>
+      </c>
+      <c r="H51" s="4">
+        <v>2</v>
+      </c>
+      <c r="I51" s="4">
+        <v>5</v>
+      </c>
+      <c r="J51" s="4">
+        <v>2</v>
+      </c>
+      <c r="K51" s="4">
+        <v>4</v>
+      </c>
+      <c r="L51" s="4">
+        <v>8</v>
+      </c>
+      <c r="M51" s="4">
+        <v>8</v>
+      </c>
+      <c r="N51" s="4">
+        <v>8</v>
+      </c>
+      <c r="O51" s="4">
+        <v>9</v>
+      </c>
+      <c r="P51" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q51" s="4">
+        <f t="shared" si="2"/>
+        <v>54</v>
+      </c>
+      <c r="R51" s="4">
+        <f t="shared" si="3"/>
+        <v>77.142857142857153</v>
+      </c>
       <c r="S51" s="4"/>
-    </row>
-    <row r="52" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T51" s="4"/>
+    </row>
+    <row r="52" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A52" s="9">
         <v>45</v>
       </c>
@@ -7212,22 +8499,51 @@
       <c r="E52" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
-      <c r="O52" s="4"/>
-      <c r="P52" s="4"/>
-      <c r="Q52" s="4"/>
-      <c r="R52" s="4"/>
+      <c r="F52" s="4">
+        <v>5</v>
+      </c>
+      <c r="G52" s="4">
+        <v>4</v>
+      </c>
+      <c r="H52" s="4">
+        <v>4</v>
+      </c>
+      <c r="I52" s="4">
+        <v>5</v>
+      </c>
+      <c r="J52" s="4">
+        <v>4</v>
+      </c>
+      <c r="K52" s="4">
+        <v>4</v>
+      </c>
+      <c r="L52" s="4">
+        <v>9</v>
+      </c>
+      <c r="M52" s="4">
+        <v>9</v>
+      </c>
+      <c r="N52" s="4">
+        <v>9</v>
+      </c>
+      <c r="O52" s="4">
+        <v>10</v>
+      </c>
+      <c r="P52" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q52" s="4">
+        <f t="shared" si="2"/>
+        <v>63</v>
+      </c>
+      <c r="R52" s="4">
+        <f t="shared" si="3"/>
+        <v>90</v>
+      </c>
       <c r="S52" s="4"/>
-    </row>
-    <row r="53" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T52" s="4"/>
+    </row>
+    <row r="53" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A53" s="11">
         <v>46</v>
       </c>
@@ -7243,22 +8559,51 @@
       <c r="E53" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
-      <c r="P53" s="4"/>
-      <c r="Q53" s="4"/>
-      <c r="R53" s="4"/>
+      <c r="F53" s="4">
+        <v>5</v>
+      </c>
+      <c r="G53" s="4">
+        <v>5</v>
+      </c>
+      <c r="H53" s="4">
+        <v>5</v>
+      </c>
+      <c r="I53" s="4">
+        <v>5</v>
+      </c>
+      <c r="J53" s="4">
+        <v>5</v>
+      </c>
+      <c r="K53" s="4">
+        <v>5</v>
+      </c>
+      <c r="L53" s="4">
+        <v>9</v>
+      </c>
+      <c r="M53" s="4">
+        <v>10</v>
+      </c>
+      <c r="N53" s="4">
+        <v>9</v>
+      </c>
+      <c r="O53" s="4">
+        <v>10</v>
+      </c>
+      <c r="P53" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q53" s="4">
+        <f t="shared" si="2"/>
+        <v>68</v>
+      </c>
+      <c r="R53" s="4">
+        <f t="shared" si="3"/>
+        <v>97.142857142857139</v>
+      </c>
       <c r="S53" s="4"/>
-    </row>
-    <row r="54" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T53" s="4"/>
+    </row>
+    <row r="54" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A54" s="9">
         <v>47</v>
       </c>
@@ -7274,22 +8619,51 @@
       <c r="E54" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
-      <c r="N54" s="4"/>
-      <c r="O54" s="4"/>
-      <c r="P54" s="4"/>
-      <c r="Q54" s="4"/>
-      <c r="R54" s="4"/>
+      <c r="F54" s="4">
+        <v>5</v>
+      </c>
+      <c r="G54" s="4">
+        <v>4</v>
+      </c>
+      <c r="H54" s="4">
+        <v>5</v>
+      </c>
+      <c r="I54" s="4">
+        <v>5</v>
+      </c>
+      <c r="J54" s="4">
+        <v>5</v>
+      </c>
+      <c r="K54" s="4">
+        <v>4</v>
+      </c>
+      <c r="L54" s="4">
+        <v>9</v>
+      </c>
+      <c r="M54" s="4">
+        <v>9</v>
+      </c>
+      <c r="N54" s="4">
+        <v>9</v>
+      </c>
+      <c r="O54" s="4">
+        <v>9</v>
+      </c>
+      <c r="P54" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q54" s="4">
+        <f t="shared" si="2"/>
+        <v>64</v>
+      </c>
+      <c r="R54" s="4">
+        <f t="shared" si="3"/>
+        <v>91.428571428571431</v>
+      </c>
       <c r="S54" s="4"/>
-    </row>
-    <row r="55" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T54" s="4"/>
+    </row>
+    <row r="55" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A55" s="11">
         <v>48</v>
       </c>
@@ -7305,22 +8679,51 @@
       <c r="E55" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="4"/>
-      <c r="L55" s="4"/>
-      <c r="M55" s="4"/>
-      <c r="N55" s="4"/>
-      <c r="O55" s="4"/>
-      <c r="P55" s="4"/>
-      <c r="Q55" s="4"/>
-      <c r="R55" s="4"/>
+      <c r="F55" s="4">
+        <v>5</v>
+      </c>
+      <c r="G55" s="4">
+        <v>4</v>
+      </c>
+      <c r="H55" s="4">
+        <v>5</v>
+      </c>
+      <c r="I55" s="4">
+        <v>5</v>
+      </c>
+      <c r="J55" s="4">
+        <v>4</v>
+      </c>
+      <c r="K55" s="4">
+        <v>4</v>
+      </c>
+      <c r="L55" s="4">
+        <v>8</v>
+      </c>
+      <c r="M55" s="4">
+        <v>9</v>
+      </c>
+      <c r="N55" s="4">
+        <v>8</v>
+      </c>
+      <c r="O55" s="4">
+        <v>9</v>
+      </c>
+      <c r="P55" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q55" s="4">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="R55" s="4">
+        <f t="shared" si="3"/>
+        <v>87.142857142857139</v>
+      </c>
       <c r="S55" s="4"/>
-    </row>
-    <row r="56" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T55" s="4"/>
+    </row>
+    <row r="56" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A56" s="9">
         <v>49</v>
       </c>
@@ -7336,22 +8739,51 @@
       <c r="E56" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4"/>
-      <c r="O56" s="4"/>
-      <c r="P56" s="4"/>
-      <c r="Q56" s="4"/>
-      <c r="R56" s="4"/>
+      <c r="F56" s="4">
+        <v>5</v>
+      </c>
+      <c r="G56" s="4">
+        <v>5</v>
+      </c>
+      <c r="H56" s="4">
+        <v>5</v>
+      </c>
+      <c r="I56" s="4">
+        <v>5</v>
+      </c>
+      <c r="J56" s="4">
+        <v>5</v>
+      </c>
+      <c r="K56" s="4">
+        <v>5</v>
+      </c>
+      <c r="L56" s="4">
+        <v>9</v>
+      </c>
+      <c r="M56" s="4">
+        <v>10</v>
+      </c>
+      <c r="N56" s="4">
+        <v>7</v>
+      </c>
+      <c r="O56" s="4">
+        <v>10</v>
+      </c>
+      <c r="P56" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q56" s="4">
+        <f t="shared" si="2"/>
+        <v>66</v>
+      </c>
+      <c r="R56" s="4">
+        <f t="shared" si="3"/>
+        <v>94.285714285714278</v>
+      </c>
       <c r="S56" s="4"/>
-    </row>
-    <row r="57" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T56" s="4"/>
+    </row>
+    <row r="57" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A57" s="11">
         <v>50</v>
       </c>
@@ -7367,22 +8799,51 @@
       <c r="E57" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
-      <c r="L57" s="4"/>
-      <c r="M57" s="4"/>
-      <c r="N57" s="4"/>
-      <c r="O57" s="4"/>
-      <c r="P57" s="4"/>
-      <c r="Q57" s="4"/>
-      <c r="R57" s="4"/>
+      <c r="F57" s="4">
+        <v>5</v>
+      </c>
+      <c r="G57" s="4">
+        <v>5</v>
+      </c>
+      <c r="H57" s="4">
+        <v>5</v>
+      </c>
+      <c r="I57" s="4">
+        <v>5</v>
+      </c>
+      <c r="J57" s="4">
+        <v>5</v>
+      </c>
+      <c r="K57" s="4">
+        <v>5</v>
+      </c>
+      <c r="L57" s="4">
+        <v>9</v>
+      </c>
+      <c r="M57" s="4">
+        <v>10</v>
+      </c>
+      <c r="N57" s="4">
+        <v>8</v>
+      </c>
+      <c r="O57" s="4">
+        <v>10</v>
+      </c>
+      <c r="P57" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q57" s="4">
+        <f t="shared" si="2"/>
+        <v>67</v>
+      </c>
+      <c r="R57" s="4">
+        <f t="shared" si="3"/>
+        <v>95.714285714285722</v>
+      </c>
       <c r="S57" s="4"/>
-    </row>
-    <row r="58" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T57" s="4"/>
+    </row>
+    <row r="58" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A58" s="9">
         <v>51</v>
       </c>
@@ -7394,22 +8855,51 @@
       <c r="E58" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
-      <c r="L58" s="4"/>
-      <c r="M58" s="4"/>
-      <c r="N58" s="4"/>
-      <c r="O58" s="4"/>
-      <c r="P58" s="4"/>
-      <c r="Q58" s="4"/>
-      <c r="R58" s="4"/>
+      <c r="F58" s="4">
+        <v>5</v>
+      </c>
+      <c r="G58" s="4">
+        <v>4</v>
+      </c>
+      <c r="H58" s="4">
+        <v>5</v>
+      </c>
+      <c r="I58" s="4">
+        <v>5</v>
+      </c>
+      <c r="J58" s="4">
+        <v>4</v>
+      </c>
+      <c r="K58" s="4">
+        <v>4</v>
+      </c>
+      <c r="L58" s="4">
+        <v>9</v>
+      </c>
+      <c r="M58" s="4">
+        <v>9</v>
+      </c>
+      <c r="N58" s="4">
+        <v>9</v>
+      </c>
+      <c r="O58" s="4">
+        <v>10</v>
+      </c>
+      <c r="P58" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q58" s="4">
+        <f t="shared" si="2"/>
+        <v>64</v>
+      </c>
+      <c r="R58" s="4">
+        <f t="shared" si="3"/>
+        <v>91.428571428571431</v>
+      </c>
       <c r="S58" s="4"/>
-    </row>
-    <row r="59" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T58" s="4"/>
+    </row>
+    <row r="59" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A59" s="11">
         <v>52</v>
       </c>
@@ -7423,22 +8913,51 @@
       <c r="E59" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="4"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="4"/>
-      <c r="L59" s="4"/>
-      <c r="M59" s="4"/>
-      <c r="N59" s="4"/>
-      <c r="O59" s="4"/>
-      <c r="P59" s="4"/>
-      <c r="Q59" s="4"/>
-      <c r="R59" s="4"/>
+      <c r="F59" s="4">
+        <v>5</v>
+      </c>
+      <c r="G59" s="4">
+        <v>4</v>
+      </c>
+      <c r="H59" s="4">
+        <v>5</v>
+      </c>
+      <c r="I59" s="4">
+        <v>5</v>
+      </c>
+      <c r="J59" s="4">
+        <v>4</v>
+      </c>
+      <c r="K59" s="4">
+        <v>4</v>
+      </c>
+      <c r="L59" s="4">
+        <v>9</v>
+      </c>
+      <c r="M59" s="4">
+        <v>9</v>
+      </c>
+      <c r="N59" s="4">
+        <v>6</v>
+      </c>
+      <c r="O59" s="4">
+        <v>10</v>
+      </c>
+      <c r="P59" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q59" s="4">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="R59" s="4">
+        <f t="shared" si="3"/>
+        <v>87.142857142857139</v>
+      </c>
       <c r="S59" s="4"/>
-    </row>
-    <row r="60" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T59" s="4"/>
+    </row>
+    <row r="60" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A60" s="9">
         <v>53</v>
       </c>
@@ -7450,22 +8969,51 @@
       <c r="E60" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="4"/>
-      <c r="L60" s="4"/>
-      <c r="M60" s="4"/>
-      <c r="N60" s="4"/>
-      <c r="O60" s="4"/>
-      <c r="P60" s="4"/>
-      <c r="Q60" s="4"/>
-      <c r="R60" s="4"/>
+      <c r="F60" s="4">
+        <v>5</v>
+      </c>
+      <c r="G60" s="4">
+        <v>5</v>
+      </c>
+      <c r="H60" s="4">
+        <v>5</v>
+      </c>
+      <c r="I60" s="4">
+        <v>5</v>
+      </c>
+      <c r="J60" s="4">
+        <v>5</v>
+      </c>
+      <c r="K60" s="4">
+        <v>5</v>
+      </c>
+      <c r="L60" s="4">
+        <v>9</v>
+      </c>
+      <c r="M60" s="4">
+        <v>9</v>
+      </c>
+      <c r="N60" s="4">
+        <v>6</v>
+      </c>
+      <c r="O60" s="4">
+        <v>10</v>
+      </c>
+      <c r="P60" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q60" s="4">
+        <f t="shared" si="2"/>
+        <v>64</v>
+      </c>
+      <c r="R60" s="4">
+        <f t="shared" si="3"/>
+        <v>91.428571428571431</v>
+      </c>
       <c r="S60" s="4"/>
-    </row>
-    <row r="61" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T60" s="4"/>
+    </row>
+    <row r="61" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A61" s="11">
         <v>54</v>
       </c>
@@ -7481,22 +9029,51 @@
       <c r="E61" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
-      <c r="J61" s="4"/>
-      <c r="K61" s="4"/>
-      <c r="L61" s="4"/>
-      <c r="M61" s="4"/>
-      <c r="N61" s="4"/>
-      <c r="O61" s="4"/>
-      <c r="P61" s="4"/>
-      <c r="Q61" s="4"/>
-      <c r="R61" s="4"/>
+      <c r="F61" s="4">
+        <v>5</v>
+      </c>
+      <c r="G61" s="4">
+        <v>5</v>
+      </c>
+      <c r="H61" s="4">
+        <v>5</v>
+      </c>
+      <c r="I61" s="4">
+        <v>5</v>
+      </c>
+      <c r="J61" s="4">
+        <v>4</v>
+      </c>
+      <c r="K61" s="4">
+        <v>4</v>
+      </c>
+      <c r="L61" s="4">
+        <v>9</v>
+      </c>
+      <c r="M61" s="4">
+        <v>9</v>
+      </c>
+      <c r="N61" s="4">
+        <v>9</v>
+      </c>
+      <c r="O61" s="4">
+        <v>8</v>
+      </c>
+      <c r="P61" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q61" s="4">
+        <f t="shared" si="2"/>
+        <v>63</v>
+      </c>
+      <c r="R61" s="4">
+        <f t="shared" si="3"/>
+        <v>90</v>
+      </c>
       <c r="S61" s="4"/>
-    </row>
-    <row r="62" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T61" s="4"/>
+    </row>
+    <row r="62" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A62" s="9">
         <v>55</v>
       </c>
@@ -7512,22 +9089,51 @@
       <c r="E62" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="4"/>
-      <c r="L62" s="4"/>
-      <c r="M62" s="4"/>
-      <c r="N62" s="4"/>
-      <c r="O62" s="4"/>
-      <c r="P62" s="4"/>
-      <c r="Q62" s="4"/>
-      <c r="R62" s="4"/>
+      <c r="F62" s="4">
+        <v>4</v>
+      </c>
+      <c r="G62" s="4">
+        <v>4</v>
+      </c>
+      <c r="H62" s="4">
+        <v>3</v>
+      </c>
+      <c r="I62" s="4">
+        <v>3</v>
+      </c>
+      <c r="J62" s="4">
+        <v>3</v>
+      </c>
+      <c r="K62" s="4">
+        <v>3</v>
+      </c>
+      <c r="L62" s="4">
+        <v>8</v>
+      </c>
+      <c r="M62" s="4">
+        <v>8</v>
+      </c>
+      <c r="N62" s="4">
+        <v>9</v>
+      </c>
+      <c r="O62" s="4">
+        <v>7</v>
+      </c>
+      <c r="P62" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q62" s="4">
+        <f t="shared" si="2"/>
+        <v>52</v>
+      </c>
+      <c r="R62" s="4">
+        <f t="shared" si="3"/>
+        <v>74.285714285714292</v>
+      </c>
       <c r="S62" s="4"/>
-    </row>
-    <row r="63" spans="1:19" s="17" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T62" s="4"/>
+    </row>
+    <row r="63" spans="1:20" s="17" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="16">
         <v>56</v>
       </c>
@@ -7539,33 +9145,62 @@
       <c r="E63" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="4"/>
-      <c r="L63" s="4"/>
-      <c r="M63" s="4"/>
-      <c r="N63" s="4"/>
-      <c r="O63" s="4"/>
-      <c r="P63" s="4"/>
-      <c r="Q63" s="4"/>
-      <c r="R63" s="4"/>
+      <c r="F63" s="4">
+        <v>4</v>
+      </c>
+      <c r="G63" s="4">
+        <v>5</v>
+      </c>
+      <c r="H63" s="4">
+        <v>4</v>
+      </c>
+      <c r="I63" s="4">
+        <v>5</v>
+      </c>
+      <c r="J63" s="4">
+        <v>4</v>
+      </c>
+      <c r="K63" s="4">
+        <v>4</v>
+      </c>
+      <c r="L63" s="4">
+        <v>9</v>
+      </c>
+      <c r="M63" s="4">
+        <v>9</v>
+      </c>
+      <c r="N63" s="4">
+        <v>7</v>
+      </c>
+      <c r="O63" s="4">
+        <v>10</v>
+      </c>
+      <c r="P63" s="4">
+        <v>70</v>
+      </c>
+      <c r="Q63" s="4">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="R63" s="4">
+        <f t="shared" si="3"/>
+        <v>87.142857142857139</v>
+      </c>
       <c r="S63" s="4"/>
+      <c r="T63" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A6:S6"/>
-    <mergeCell ref="A32:S32"/>
-    <mergeCell ref="P3:P5"/>
+    <mergeCell ref="A6:T6"/>
+    <mergeCell ref="A32:T32"/>
     <mergeCell ref="Q3:Q5"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A2:S2"/>
-    <mergeCell ref="F3:N3"/>
-    <mergeCell ref="O3:O4"/>
     <mergeCell ref="R3:R5"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="F3:O3"/>
+    <mergeCell ref="P3:P4"/>
     <mergeCell ref="S3:S5"/>
+    <mergeCell ref="T3:T5"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
@@ -7594,91 +9229,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="32" t="s">
+      <c r="C3" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="36" t="s">
+      <c r="E3" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="32" t="s">
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="32" t="s">
+      <c r="M3" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="32" t="s">
+      <c r="N3" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="32" t="s">
+      <c r="O3" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="32" t="s">
+      <c r="P3" s="34" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="34"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="36"/>
       <c r="F4" s="2" t="s">
         <v>278</v>
       </c>
@@ -7697,18 +9332,18 @@
       <c r="K4" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
-      <c r="P4" s="32"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="34"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="32"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="35"/>
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="37"/>
       <c r="F5" s="3">
         <v>100</v>
       </c>
@@ -7730,30 +9365,30 @@
       <c r="L5" s="3">
         <v>500</v>
       </c>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="32"/>
-      <c r="P5" s="32"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="34"/>
+      <c r="P5" s="34"/>
     </row>
     <row r="6" spans="1:16" ht="21" x14ac:dyDescent="0.35">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="39" t="s">
         <v>225</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="39"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="41"/>
     </row>
     <row r="7" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18">
@@ -7769,7 +9404,9 @@
       <c r="E7" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F7" s="4"/>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -8588,24 +10225,24 @@
       <c r="P38" s="4"/>
     </row>
     <row r="39" spans="1:16" ht="21" x14ac:dyDescent="0.35">
-      <c r="A39" s="37" t="s">
+      <c r="A39" s="39" t="s">
         <v>183</v>
       </c>
-      <c r="B39" s="38"/>
-      <c r="C39" s="38"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="38"/>
-      <c r="G39" s="38"/>
-      <c r="H39" s="38"/>
-      <c r="I39" s="38"/>
-      <c r="J39" s="38"/>
-      <c r="K39" s="38"/>
-      <c r="L39" s="38"/>
-      <c r="M39" s="38"/>
-      <c r="N39" s="38"/>
-      <c r="O39" s="38"/>
-      <c r="P39" s="39"/>
+      <c r="B39" s="40"/>
+      <c r="C39" s="40"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="40"/>
+      <c r="I39" s="40"/>
+      <c r="J39" s="40"/>
+      <c r="K39" s="40"/>
+      <c r="L39" s="40"/>
+      <c r="M39" s="40"/>
+      <c r="N39" s="40"/>
+      <c r="O39" s="40"/>
+      <c r="P39" s="41"/>
     </row>
     <row r="40" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="18">
@@ -9233,6 +10870,8 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:P6"/>
+    <mergeCell ref="A39:P39"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A3:A5"/>
@@ -9246,8 +10885,6 @@
     <mergeCell ref="N3:N5"/>
     <mergeCell ref="O3:O5"/>
     <mergeCell ref="P3:P5"/>
-    <mergeCell ref="A6:P6"/>
-    <mergeCell ref="A39:P39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9267,91 +10904,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="32" t="s">
+      <c r="C3" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="36" t="s">
+      <c r="E3" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="32" t="s">
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="32" t="s">
+      <c r="M3" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="32" t="s">
+      <c r="N3" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="32" t="s">
+      <c r="O3" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="32" t="s">
+      <c r="P3" s="34" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
       <c r="F4" s="2" t="s">
         <v>278</v>
       </c>
@@ -9370,18 +11007,18 @@
       <c r="K4" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
-      <c r="P4" s="32"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="34"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="32"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
       <c r="F5" s="3">
         <v>5</v>
       </c>
@@ -9403,30 +11040,30 @@
       <c r="L5" s="3">
         <v>25</v>
       </c>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="32"/>
-      <c r="P5" s="32"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="34"/>
+      <c r="P5" s="34"/>
     </row>
     <row r="6" spans="1:16" ht="21" x14ac:dyDescent="0.35">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="45" t="s">
         <v>183</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="43"/>
-      <c r="M6" s="43"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="45"/>
+      <c r="P6" s="45"/>
     </row>
     <row r="7" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
@@ -10677,24 +12314,24 @@
       <c r="P32" s="4"/>
     </row>
     <row r="33" spans="1:16" ht="21" x14ac:dyDescent="0.35">
-      <c r="A33" s="43" t="s">
+      <c r="A33" s="45" t="s">
         <v>225</v>
       </c>
-      <c r="B33" s="43"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="43"/>
-      <c r="H33" s="43"/>
-      <c r="I33" s="43"/>
-      <c r="J33" s="43"/>
-      <c r="K33" s="43"/>
-      <c r="L33" s="43"/>
-      <c r="M33" s="43"/>
-      <c r="N33" s="43"/>
-      <c r="O33" s="43"/>
-      <c r="P33" s="43"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="45"/>
+      <c r="I33" s="45"/>
+      <c r="J33" s="45"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="45"/>
+      <c r="M33" s="45"/>
+      <c r="N33" s="45"/>
+      <c r="O33" s="45"/>
+      <c r="P33" s="45"/>
     </row>
     <row r="34" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
@@ -11946,6 +13583,8 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:P6"/>
+    <mergeCell ref="A33:P33"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A3:A5"/>
@@ -11959,8 +13598,6 @@
     <mergeCell ref="N3:N5"/>
     <mergeCell ref="O3:O5"/>
     <mergeCell ref="P3:P5"/>
-    <mergeCell ref="A6:P6"/>
-    <mergeCell ref="A33:P33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11978,94 +13615,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="31"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="32" t="s">
+      <c r="C3" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="36" t="s">
+      <c r="E3" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="32" t="s">
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="N3" s="32" t="s">
+      <c r="N3" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="32" t="s">
+      <c r="O3" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="32" t="s">
+      <c r="P3" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="32" t="s">
+      <c r="Q3" s="34" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
       <c r="F4" s="2" t="s">
         <v>125</v>
       </c>
@@ -12087,18 +13724,18 @@
       <c r="L4" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
-      <c r="P4" s="32"/>
-      <c r="Q4" s="32"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="34"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="32"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
       <c r="F5" s="3">
         <v>5</v>
       </c>
@@ -12123,31 +13760,31 @@
       <c r="M5" s="3">
         <v>30</v>
       </c>
-      <c r="N5" s="32"/>
-      <c r="O5" s="32"/>
-      <c r="P5" s="32"/>
-      <c r="Q5" s="32"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="34"/>
+      <c r="P5" s="34"/>
+      <c r="Q5" s="34"/>
     </row>
     <row r="6" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="45" t="s">
         <v>225</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="43"/>
-      <c r="M6" s="43"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="43"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="45"/>
+      <c r="P6" s="45"/>
+      <c r="Q6" s="45"/>
     </row>
     <row r="7" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
@@ -13629,25 +15266,25 @@
       <c r="Q35" s="4"/>
     </row>
     <row r="36" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A36" s="43" t="s">
+      <c r="A36" s="45" t="s">
         <v>183</v>
       </c>
-      <c r="B36" s="43"/>
-      <c r="C36" s="43"/>
-      <c r="D36" s="43"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="43"/>
-      <c r="I36" s="43"/>
-      <c r="J36" s="43"/>
-      <c r="K36" s="43"/>
-      <c r="L36" s="43"/>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
-      <c r="O36" s="43"/>
-      <c r="P36" s="43"/>
-      <c r="Q36" s="43"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="45"/>
+      <c r="K36" s="45"/>
+      <c r="L36" s="45"/>
+      <c r="M36" s="45"/>
+      <c r="N36" s="45"/>
+      <c r="O36" s="45"/>
+      <c r="P36" s="45"/>
+      <c r="Q36" s="45"/>
     </row>
     <row r="37" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
@@ -14926,6 +16563,8 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:Q6"/>
+    <mergeCell ref="A36:Q36"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A3:A5"/>
@@ -14939,8 +16578,6 @@
     <mergeCell ref="O3:O5"/>
     <mergeCell ref="P3:P5"/>
     <mergeCell ref="Q3:Q5"/>
-    <mergeCell ref="A6:Q6"/>
-    <mergeCell ref="A36:Q36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14957,80 +16594,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="36" t="s">
+      <c r="C3" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="32" t="s">
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="32" t="s">
+      <c r="L3" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="32" t="s">
+      <c r="M3" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="N3" s="32" t="s">
+      <c r="N3" s="34" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="35.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="34"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="36"/>
       <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
@@ -15049,16 +16686,16 @@
       <c r="J4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="32"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="35"/>
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="37"/>
       <c r="E5" s="3">
         <v>25</v>
       </c>
@@ -15081,9 +16718,9 @@
         <f>SUM(E5:J5)</f>
         <v>150</v>
       </c>
-      <c r="L5" s="32"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
     </row>
     <row r="6" spans="1:14" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
@@ -15118,7 +16755,7 @@
         <v>150</v>
       </c>
       <c r="L6" s="4">
-        <f>SUM(E6:J6)</f>
+        <f t="shared" ref="L6:L43" si="0">SUM(E6:J6)</f>
         <v>99</v>
       </c>
       <c r="M6" s="8">
@@ -15160,11 +16797,11 @@
         <v>150</v>
       </c>
       <c r="L7" s="4">
-        <f>SUM(E7:J7)</f>
+        <f t="shared" si="0"/>
         <v>75</v>
       </c>
       <c r="M7" s="8">
-        <f t="shared" ref="M7:M49" si="0">L7/K7*100</f>
+        <f t="shared" ref="M7:M49" si="1">L7/K7*100</f>
         <v>50</v>
       </c>
       <c r="N7" s="4"/>
@@ -15202,11 +16839,11 @@
         <v>150</v>
       </c>
       <c r="L8" s="4">
-        <f>SUM(E8:J8)</f>
+        <f t="shared" si="0"/>
         <v>118</v>
       </c>
       <c r="M8" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>78.666666666666657</v>
       </c>
       <c r="N8" s="4"/>
@@ -15244,11 +16881,11 @@
         <v>150</v>
       </c>
       <c r="L9" s="4">
-        <f>SUM(E9:J9)</f>
+        <f t="shared" si="0"/>
         <v>77</v>
       </c>
       <c r="M9" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>51.333333333333329</v>
       </c>
       <c r="N9" s="4"/>
@@ -15286,11 +16923,11 @@
         <v>150</v>
       </c>
       <c r="L10" s="4">
-        <f>SUM(E10:J10)</f>
+        <f t="shared" si="0"/>
         <v>83</v>
       </c>
       <c r="M10" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>55.333333333333336</v>
       </c>
       <c r="N10" s="4"/>
@@ -15328,11 +16965,11 @@
         <v>150</v>
       </c>
       <c r="L11" s="4">
-        <f>SUM(E11:J11)</f>
+        <f t="shared" si="0"/>
         <v>65</v>
       </c>
       <c r="M11" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>43.333333333333336</v>
       </c>
       <c r="N11" s="4"/>
@@ -15370,11 +17007,11 @@
         <v>150</v>
       </c>
       <c r="L12" s="4">
-        <f>SUM(E12:J12)</f>
+        <f t="shared" si="0"/>
         <v>88.5</v>
       </c>
       <c r="M12" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>59</v>
       </c>
       <c r="N12" s="4"/>
@@ -15412,11 +17049,11 @@
         <v>150</v>
       </c>
       <c r="L13" s="4">
-        <f>SUM(E13:J13)</f>
+        <f t="shared" si="0"/>
         <v>132</v>
       </c>
       <c r="M13" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>88</v>
       </c>
       <c r="N13" s="4"/>
@@ -15454,11 +17091,11 @@
         <v>150</v>
       </c>
       <c r="L14" s="4">
-        <f>SUM(E14:J14)</f>
+        <f t="shared" si="0"/>
         <v>128</v>
       </c>
       <c r="M14" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>85.333333333333343</v>
       </c>
       <c r="N14" s="4"/>
@@ -15496,11 +17133,11 @@
         <v>150</v>
       </c>
       <c r="L15" s="4">
-        <f>SUM(E15:J15)</f>
+        <f t="shared" si="0"/>
         <v>112</v>
       </c>
       <c r="M15" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>74.666666666666671</v>
       </c>
       <c r="N15" s="4"/>
@@ -15538,11 +17175,11 @@
         <v>150</v>
       </c>
       <c r="L16" s="4">
-        <f>SUM(E16:J16)</f>
+        <f t="shared" si="0"/>
         <v>69</v>
       </c>
       <c r="M16" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="N16" s="4"/>
@@ -15580,11 +17217,11 @@
         <v>150</v>
       </c>
       <c r="L17" s="4">
-        <f>SUM(E17:J17)</f>
+        <f t="shared" si="0"/>
         <v>104.5</v>
       </c>
       <c r="M17" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>69.666666666666671</v>
       </c>
       <c r="N17" s="4"/>
@@ -15622,11 +17259,11 @@
         <v>150</v>
       </c>
       <c r="L18" s="4">
-        <f>SUM(E18:J18)</f>
+        <f t="shared" si="0"/>
         <v>118</v>
       </c>
       <c r="M18" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>78.666666666666657</v>
       </c>
       <c r="N18" s="4"/>
@@ -15664,11 +17301,11 @@
         <v>150</v>
       </c>
       <c r="L19" s="4">
-        <f>SUM(E19:J19)</f>
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="M19" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="N19" s="4"/>
@@ -15706,11 +17343,11 @@
         <v>150</v>
       </c>
       <c r="L20" s="4">
-        <f>SUM(E20:J20)</f>
+        <f t="shared" si="0"/>
         <v>113.5</v>
       </c>
       <c r="M20" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>75.666666666666671</v>
       </c>
       <c r="N20" s="4"/>
@@ -15748,11 +17385,11 @@
         <v>150</v>
       </c>
       <c r="L21" s="4">
-        <f>SUM(E21:J21)</f>
+        <f t="shared" si="0"/>
         <v>92.5</v>
       </c>
       <c r="M21" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>61.666666666666671</v>
       </c>
       <c r="N21" s="4"/>
@@ -15790,11 +17427,11 @@
         <v>150</v>
       </c>
       <c r="L22" s="4">
-        <f>SUM(E22:J22)</f>
+        <f t="shared" si="0"/>
         <v>122.5</v>
       </c>
       <c r="M22" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>81.666666666666671</v>
       </c>
       <c r="N22" s="4"/>
@@ -15832,11 +17469,11 @@
         <v>150</v>
       </c>
       <c r="L23" s="4">
-        <f>SUM(E23:J23)</f>
+        <f t="shared" si="0"/>
         <v>126</v>
       </c>
       <c r="M23" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>84</v>
       </c>
       <c r="N23" s="4"/>
@@ -15874,11 +17511,11 @@
         <v>150</v>
       </c>
       <c r="L24" s="4">
-        <f>SUM(E24:J24)</f>
+        <f t="shared" si="0"/>
         <v>102.5</v>
       </c>
       <c r="M24" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>68.333333333333329</v>
       </c>
       <c r="N24" s="4"/>
@@ -15916,11 +17553,11 @@
         <v>150</v>
       </c>
       <c r="L25" s="4">
-        <f>SUM(E25:J25)</f>
+        <f t="shared" si="0"/>
         <v>89</v>
       </c>
       <c r="M25" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>59.333333333333336</v>
       </c>
       <c r="N25" s="4"/>
@@ -15958,11 +17595,11 @@
         <v>150</v>
       </c>
       <c r="L26" s="4">
-        <f>SUM(E26:J26)</f>
+        <f t="shared" si="0"/>
         <v>89.5</v>
       </c>
       <c r="M26" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>59.666666666666671</v>
       </c>
       <c r="N26" s="4"/>
@@ -16000,11 +17637,11 @@
         <v>150</v>
       </c>
       <c r="L27" s="4">
-        <f>SUM(E27:J27)</f>
+        <f t="shared" si="0"/>
         <v>92</v>
       </c>
       <c r="M27" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>61.333333333333329</v>
       </c>
       <c r="N27" s="4"/>
@@ -16042,11 +17679,11 @@
         <v>150</v>
       </c>
       <c r="L28" s="4">
-        <f>SUM(E28:J28)</f>
+        <f t="shared" si="0"/>
         <v>80</v>
       </c>
       <c r="M28" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>53.333333333333336</v>
       </c>
       <c r="N28" s="4"/>
@@ -16084,11 +17721,11 @@
         <v>150</v>
       </c>
       <c r="L29" s="4">
-        <f>SUM(E29:J29)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M29" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N29" s="4"/>
@@ -16126,11 +17763,11 @@
         <v>150</v>
       </c>
       <c r="L30" s="4">
-        <f>SUM(E30:J30)</f>
+        <f t="shared" si="0"/>
         <v>80</v>
       </c>
       <c r="M30" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>53.333333333333336</v>
       </c>
       <c r="N30" s="4"/>
@@ -16168,11 +17805,11 @@
         <v>150</v>
       </c>
       <c r="L31" s="4">
-        <f>SUM(E31:J31)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="M31" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.666666666666667</v>
       </c>
       <c r="N31" s="4"/>
@@ -16194,11 +17831,11 @@
         <v>150</v>
       </c>
       <c r="L32" s="4">
-        <f>SUM(E32:J32)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M32" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N32" s="4"/>
@@ -16236,11 +17873,11 @@
         <v>150</v>
       </c>
       <c r="L33" s="4">
-        <f>SUM(E33:J33)</f>
+        <f t="shared" si="0"/>
         <v>101.5</v>
       </c>
       <c r="M33" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>67.666666666666657</v>
       </c>
       <c r="N33" s="4"/>
@@ -16278,11 +17915,11 @@
         <v>150</v>
       </c>
       <c r="L34" s="4">
-        <f>SUM(E34:J34)</f>
+        <f t="shared" si="0"/>
         <v>95.5</v>
       </c>
       <c r="M34" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>63.666666666666671</v>
       </c>
       <c r="N34" s="4"/>
@@ -16320,11 +17957,11 @@
         <v>150</v>
       </c>
       <c r="L35" s="4">
-        <f>SUM(E35:J35)</f>
+        <f t="shared" si="0"/>
         <v>92</v>
       </c>
       <c r="M35" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>61.333333333333329</v>
       </c>
       <c r="N35" s="4"/>
@@ -16362,11 +17999,11 @@
         <v>150</v>
       </c>
       <c r="L36" s="4">
-        <f>SUM(E36:J36)</f>
+        <f t="shared" si="0"/>
         <v>101</v>
       </c>
       <c r="M36" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>67.333333333333329</v>
       </c>
       <c r="N36" s="4"/>
@@ -16404,11 +18041,11 @@
         <v>150</v>
       </c>
       <c r="L37" s="4">
-        <f>SUM(E37:J37)</f>
+        <f t="shared" si="0"/>
         <v>78</v>
       </c>
       <c r="M37" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>52</v>
       </c>
       <c r="N37" s="4"/>
@@ -16446,11 +18083,11 @@
         <v>150</v>
       </c>
       <c r="L38" s="4">
-        <f>SUM(E38:J38)</f>
+        <f t="shared" si="0"/>
         <v>45.5</v>
       </c>
       <c r="M38" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30.333333333333336</v>
       </c>
       <c r="N38" s="4"/>
@@ -16488,434 +18125,434 @@
         <v>150</v>
       </c>
       <c r="L39" s="4">
-        <f>SUM(E39:J39)</f>
+        <f t="shared" si="0"/>
         <v>103</v>
       </c>
       <c r="M39" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>68.666666666666671</v>
       </c>
       <c r="N39" s="4"/>
     </row>
-    <row r="40" spans="1:14" s="46" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" s="32" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>35</v>
       </c>
-      <c r="B40" s="45"/>
-      <c r="C40" s="44" t="s">
+      <c r="B40" s="31"/>
+      <c r="C40" s="5" t="s">
         <v>533</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E40" s="45">
+      <c r="E40" s="31">
         <v>24</v>
       </c>
-      <c r="F40" s="45">
+      <c r="F40" s="31">
         <v>25</v>
       </c>
-      <c r="G40" s="45">
+      <c r="G40" s="31">
         <v>25</v>
       </c>
-      <c r="H40" s="45">
+      <c r="H40" s="31">
         <v>7</v>
       </c>
-      <c r="I40" s="45">
-        <v>0</v>
-      </c>
-      <c r="J40" s="45">
+      <c r="I40" s="31">
+        <v>0</v>
+      </c>
+      <c r="J40" s="31">
         <v>25</v>
       </c>
       <c r="K40" s="4">
         <v>150</v>
       </c>
-      <c r="L40" s="45">
-        <f>SUM(E40:J40)</f>
+      <c r="L40" s="31">
+        <f t="shared" si="0"/>
         <v>106</v>
       </c>
       <c r="M40" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>70.666666666666671</v>
       </c>
-      <c r="N40" s="45"/>
-    </row>
-    <row r="41" spans="1:14" s="46" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N40" s="31"/>
+    </row>
+    <row r="41" spans="1:14" s="32" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>36</v>
       </c>
-      <c r="B41" s="45"/>
-      <c r="C41" s="44" t="s">
+      <c r="B41" s="31"/>
+      <c r="C41" s="5" t="s">
         <v>534</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E41" s="45">
+      <c r="E41" s="31">
         <v>17</v>
       </c>
-      <c r="F41" s="45">
+      <c r="F41" s="31">
         <v>25</v>
       </c>
-      <c r="G41" s="45">
+      <c r="G41" s="31">
         <v>20</v>
       </c>
-      <c r="H41" s="45">
-        <v>5</v>
-      </c>
-      <c r="I41" s="45">
+      <c r="H41" s="31">
+        <v>5</v>
+      </c>
+      <c r="I41" s="31">
         <v>21</v>
       </c>
-      <c r="J41" s="45">
+      <c r="J41" s="31">
         <v>23</v>
       </c>
       <c r="K41" s="4">
         <v>150</v>
       </c>
-      <c r="L41" s="45">
-        <f>SUM(E41:J41)</f>
+      <c r="L41" s="31">
+        <f t="shared" si="0"/>
         <v>111</v>
       </c>
       <c r="M41" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
-      <c r="N41" s="45"/>
-    </row>
-    <row r="42" spans="1:14" s="46" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N41" s="31"/>
+    </row>
+    <row r="42" spans="1:14" s="32" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>37</v>
       </c>
-      <c r="B42" s="45"/>
-      <c r="C42" s="44" t="s">
+      <c r="B42" s="31"/>
+      <c r="C42" s="5" t="s">
         <v>535</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E42" s="45">
+      <c r="E42" s="31">
         <v>18</v>
       </c>
-      <c r="F42" s="45">
+      <c r="F42" s="31">
         <v>25</v>
       </c>
-      <c r="G42" s="45">
+      <c r="G42" s="31">
         <v>15</v>
       </c>
-      <c r="H42" s="45">
-        <v>0</v>
-      </c>
-      <c r="I42" s="45">
+      <c r="H42" s="31">
+        <v>0</v>
+      </c>
+      <c r="I42" s="31">
         <v>11</v>
       </c>
-      <c r="J42" s="45">
+      <c r="J42" s="31">
         <v>17</v>
       </c>
       <c r="K42" s="4">
         <v>150</v>
       </c>
-      <c r="L42" s="45">
-        <f>SUM(E42:J42)</f>
+      <c r="L42" s="31">
+        <f t="shared" si="0"/>
         <v>86</v>
       </c>
       <c r="M42" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>57.333333333333336</v>
       </c>
-      <c r="N42" s="45"/>
-    </row>
-    <row r="43" spans="1:14" s="46" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N42" s="31"/>
+    </row>
+    <row r="43" spans="1:14" s="32" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>38</v>
       </c>
-      <c r="B43" s="45"/>
-      <c r="C43" s="44" t="s">
+      <c r="B43" s="31"/>
+      <c r="C43" s="5" t="s">
         <v>536</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E43" s="45">
+      <c r="E43" s="31">
         <v>17.5</v>
       </c>
-      <c r="F43" s="45">
+      <c r="F43" s="31">
         <v>24</v>
       </c>
-      <c r="G43" s="45">
+      <c r="G43" s="31">
         <v>13</v>
       </c>
-      <c r="H43" s="45">
-        <v>0</v>
-      </c>
-      <c r="I43" s="45">
+      <c r="H43" s="31">
+        <v>0</v>
+      </c>
+      <c r="I43" s="31">
         <v>21</v>
       </c>
-      <c r="J43" s="45">
+      <c r="J43" s="31">
         <v>17</v>
       </c>
       <c r="K43" s="4">
         <v>150</v>
       </c>
-      <c r="L43" s="45">
-        <f>SUM(E43:J43)</f>
+      <c r="L43" s="31">
+        <f t="shared" si="0"/>
         <v>92.5</v>
       </c>
       <c r="M43" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>61.666666666666671</v>
       </c>
-      <c r="N43" s="45"/>
-    </row>
-    <row r="44" spans="1:14" s="46" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N43" s="31"/>
+    </row>
+    <row r="44" spans="1:14" s="32" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>39</v>
       </c>
-      <c r="B44" s="45"/>
-      <c r="C44" s="44" t="s">
+      <c r="B44" s="31"/>
+      <c r="C44" s="5" t="s">
         <v>130</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E44" s="45">
+      <c r="E44" s="31">
         <v>7</v>
       </c>
-      <c r="F44" s="45" t="s">
+      <c r="F44" s="31" t="s">
         <v>446</v>
       </c>
-      <c r="G44" s="45" t="s">
+      <c r="G44" s="31" t="s">
         <v>446</v>
       </c>
-      <c r="H44" s="45" t="s">
+      <c r="H44" s="31" t="s">
         <v>446</v>
       </c>
-      <c r="I44" s="45">
-        <v>0</v>
-      </c>
-      <c r="J44" s="45" t="s">
+      <c r="I44" s="31">
+        <v>0</v>
+      </c>
+      <c r="J44" s="31" t="s">
         <v>446</v>
       </c>
       <c r="K44" s="4">
         <v>150</v>
       </c>
-      <c r="L44" s="45">
-        <f t="shared" ref="L44:L49" si="1">SUM(E44:J44)</f>
+      <c r="L44" s="31">
+        <f t="shared" ref="L44:L49" si="2">SUM(E44:J44)</f>
         <v>7</v>
       </c>
       <c r="M44" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.666666666666667</v>
       </c>
-      <c r="N44" s="45"/>
-    </row>
-    <row r="45" spans="1:14" s="46" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N44" s="31"/>
+    </row>
+    <row r="45" spans="1:14" s="32" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>40</v>
       </c>
-      <c r="B45" s="45"/>
-      <c r="C45" s="44" t="s">
+      <c r="B45" s="31"/>
+      <c r="C45" s="5" t="s">
         <v>537</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E45" s="45">
+      <c r="E45" s="31">
         <v>24</v>
       </c>
-      <c r="F45" s="45">
+      <c r="F45" s="31">
         <v>25</v>
       </c>
-      <c r="G45" s="45">
+      <c r="G45" s="31">
         <v>25</v>
       </c>
-      <c r="H45" s="45">
+      <c r="H45" s="31">
         <v>9</v>
       </c>
-      <c r="I45" s="45">
+      <c r="I45" s="31">
         <v>22</v>
       </c>
-      <c r="J45" s="45">
+      <c r="J45" s="31">
         <v>25</v>
       </c>
       <c r="K45" s="4">
         <v>150</v>
       </c>
-      <c r="L45" s="45">
-        <f t="shared" si="1"/>
+      <c r="L45" s="31">
+        <f t="shared" si="2"/>
         <v>130</v>
       </c>
       <c r="M45" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>86.666666666666671</v>
       </c>
-      <c r="N45" s="45"/>
-    </row>
-    <row r="46" spans="1:14" s="46" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N45" s="31"/>
+    </row>
+    <row r="46" spans="1:14" s="32" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>41</v>
       </c>
-      <c r="B46" s="45"/>
-      <c r="C46" s="44" t="s">
+      <c r="B46" s="31"/>
+      <c r="C46" s="5" t="s">
         <v>538</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E46" s="45">
+      <c r="E46" s="31">
         <v>9.5</v>
       </c>
-      <c r="F46" s="45">
+      <c r="F46" s="31">
         <v>8.5</v>
       </c>
-      <c r="G46" s="45">
+      <c r="G46" s="31">
         <v>2</v>
       </c>
-      <c r="H46" s="45">
+      <c r="H46" s="31">
         <v>6</v>
       </c>
-      <c r="I46" s="45">
+      <c r="I46" s="31">
         <v>7</v>
       </c>
-      <c r="J46" s="45">
+      <c r="J46" s="31">
         <v>0</v>
       </c>
       <c r="K46" s="4">
         <v>150</v>
       </c>
-      <c r="L46" s="45">
-        <f t="shared" si="1"/>
+      <c r="L46" s="31">
+        <f t="shared" si="2"/>
         <v>33</v>
       </c>
       <c r="M46" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="N46" s="45"/>
-    </row>
-    <row r="47" spans="1:14" s="46" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N46" s="31"/>
+    </row>
+    <row r="47" spans="1:14" s="32" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>42</v>
       </c>
-      <c r="B47" s="45"/>
-      <c r="C47" s="44" t="s">
+      <c r="B47" s="31"/>
+      <c r="C47" s="5" t="s">
         <v>106</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E47" s="45">
+      <c r="E47" s="31">
         <v>15</v>
       </c>
-      <c r="F47" s="45">
+      <c r="F47" s="31">
         <v>17.5</v>
       </c>
-      <c r="G47" s="45">
+      <c r="G47" s="31">
         <v>2</v>
       </c>
-      <c r="H47" s="45">
+      <c r="H47" s="31">
         <v>7</v>
       </c>
-      <c r="I47" s="45" t="s">
+      <c r="I47" s="31" t="s">
         <v>446</v>
       </c>
-      <c r="J47" s="45">
+      <c r="J47" s="31">
         <v>3</v>
       </c>
       <c r="K47" s="4">
         <v>150</v>
       </c>
-      <c r="L47" s="45">
-        <f t="shared" si="1"/>
+      <c r="L47" s="31">
+        <f t="shared" si="2"/>
         <v>44.5</v>
       </c>
       <c r="M47" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29.666666666666668</v>
       </c>
-      <c r="N47" s="45"/>
-    </row>
-    <row r="48" spans="1:14" s="46" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N47" s="31"/>
+    </row>
+    <row r="48" spans="1:14" s="32" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>43</v>
       </c>
-      <c r="B48" s="45"/>
-      <c r="C48" s="44" t="s">
+      <c r="B48" s="31"/>
+      <c r="C48" s="5" t="s">
         <v>539</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E48" s="45">
+      <c r="E48" s="31">
         <v>22</v>
       </c>
-      <c r="F48" s="45">
-        <v>0</v>
-      </c>
-      <c r="G48" s="45" t="s">
+      <c r="F48" s="31">
+        <v>0</v>
+      </c>
+      <c r="G48" s="31" t="s">
         <v>446</v>
       </c>
-      <c r="H48" s="45">
-        <v>0</v>
-      </c>
-      <c r="I48" s="45">
-        <v>4</v>
-      </c>
-      <c r="J48" s="45">
+      <c r="H48" s="31">
+        <v>0</v>
+      </c>
+      <c r="I48" s="31">
+        <v>4</v>
+      </c>
+      <c r="J48" s="31">
         <v>0</v>
       </c>
       <c r="K48" s="4">
         <v>150</v>
       </c>
-      <c r="L48" s="45">
-        <f t="shared" si="1"/>
+      <c r="L48" s="31">
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
       <c r="M48" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>17.333333333333336</v>
       </c>
-      <c r="N48" s="45"/>
-    </row>
-    <row r="49" spans="1:14" s="46" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N48" s="31"/>
+    </row>
+    <row r="49" spans="1:14" s="32" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>44</v>
       </c>
-      <c r="B49" s="45"/>
-      <c r="C49" s="44" t="s">
+      <c r="B49" s="31"/>
+      <c r="C49" s="5" t="s">
         <v>540</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E49" s="45">
+      <c r="E49" s="31">
         <v>19</v>
       </c>
-      <c r="F49" s="45">
+      <c r="F49" s="31">
         <v>17</v>
       </c>
-      <c r="G49" s="45">
+      <c r="G49" s="31">
         <v>23</v>
       </c>
-      <c r="H49" s="45">
+      <c r="H49" s="31">
         <v>7</v>
       </c>
-      <c r="I49" s="45">
+      <c r="I49" s="31">
         <v>19</v>
       </c>
-      <c r="J49" s="45">
+      <c r="J49" s="31">
         <v>15</v>
       </c>
       <c r="K49" s="4">
         <v>150</v>
       </c>
-      <c r="L49" s="45">
-        <f t="shared" si="1"/>
+      <c r="L49" s="31">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="M49" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>66.666666666666657</v>
       </c>
-      <c r="N49" s="45"/>
+      <c r="N49" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -16947,77 +18584,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="36" t="s">
+      <c r="C3" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="32" t="s">
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="32" t="s">
+      <c r="K3" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="L3" s="32" t="s">
+      <c r="L3" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="M3" s="32" t="s">
+      <c r="M3" s="34" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="35.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="34"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="36"/>
       <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
@@ -17033,16 +18670,16 @@
       <c r="I4" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="32"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="35"/>
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="37"/>
       <c r="E5" s="3">
         <v>25</v>
       </c>
@@ -17062,9 +18699,9 @@
         <f>SUM(E5:I5)</f>
         <v>125</v>
       </c>
-      <c r="K5" s="32"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="32"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
     </row>
     <row r="6" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
@@ -17096,7 +18733,7 @@
         <v>125</v>
       </c>
       <c r="K6" s="4">
-        <f>SUM(E6:I6)</f>
+        <f t="shared" ref="K6:K35" si="0">SUM(E6:I6)</f>
         <v>30</v>
       </c>
       <c r="L6" s="8">
@@ -17135,11 +18772,11 @@
         <v>125</v>
       </c>
       <c r="K7" s="4">
-        <f>SUM(E7:I7)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="L7" s="8">
-        <f t="shared" ref="L7:L34" si="0">K7/J7*100</f>
+        <f t="shared" ref="L7:L34" si="1">K7/J7*100</f>
         <v>14.399999999999999</v>
       </c>
       <c r="M7" s="4"/>
@@ -17174,11 +18811,11 @@
         <v>125</v>
       </c>
       <c r="K8" s="4">
-        <f>SUM(E8:I8)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="L8" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="M8" s="4"/>
@@ -17213,11 +18850,11 @@
         <v>125</v>
       </c>
       <c r="K9" s="4">
-        <f>SUM(E9:I9)</f>
+        <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="L9" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>47.199999999999996</v>
       </c>
       <c r="M9" s="4"/>
@@ -17252,11 +18889,11 @@
         <v>125</v>
       </c>
       <c r="K10" s="4">
-        <f>SUM(E10:I10)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="L10" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12.8</v>
       </c>
       <c r="M10" s="4"/>
@@ -17291,11 +18928,11 @@
         <v>125</v>
       </c>
       <c r="K11" s="4">
-        <f>SUM(E11:I11)</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="L11" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>36.799999999999997</v>
       </c>
       <c r="M11" s="4"/>
@@ -17330,11 +18967,11 @@
         <v>125</v>
       </c>
       <c r="K12" s="4">
-        <f>SUM(E12:I12)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="L12" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.6</v>
       </c>
       <c r="M12" s="4"/>
@@ -17369,11 +19006,11 @@
         <v>125</v>
       </c>
       <c r="K13" s="4">
-        <f>SUM(E13:I13)</f>
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="L13" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>33.6</v>
       </c>
       <c r="M13" s="4"/>
@@ -17408,11 +19045,11 @@
         <v>125</v>
       </c>
       <c r="K14" s="4">
-        <f>SUM(E14:I14)</f>
+        <f t="shared" si="0"/>
         <v>65</v>
       </c>
       <c r="L14" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>52</v>
       </c>
       <c r="M14" s="4"/>
@@ -17447,11 +19084,11 @@
         <v>125</v>
       </c>
       <c r="K15" s="4">
-        <f>SUM(E15:I15)</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="L15" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="M15" s="4"/>
@@ -17486,11 +19123,11 @@
         <v>125</v>
       </c>
       <c r="K16" s="4">
-        <f>SUM(E16:I16)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="L16" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>17.599999999999998</v>
       </c>
       <c r="M16" s="4"/>
@@ -17525,11 +19162,11 @@
         <v>125</v>
       </c>
       <c r="K17" s="4">
-        <f>SUM(E17:I17)</f>
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="L17" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>33.6</v>
       </c>
       <c r="M17" s="4"/>
@@ -17564,11 +19201,11 @@
         <v>125</v>
       </c>
       <c r="K18" s="4">
-        <f>SUM(E18:I18)</f>
+        <f t="shared" si="0"/>
         <v>73</v>
       </c>
       <c r="L18" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>58.4</v>
       </c>
       <c r="M18" s="4"/>
@@ -17603,11 +19240,11 @@
         <v>125</v>
       </c>
       <c r="K19" s="4">
-        <f>SUM(E19:I19)</f>
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="L19" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>51.2</v>
       </c>
       <c r="M19" s="4"/>
@@ -17642,11 +19279,11 @@
         <v>125</v>
       </c>
       <c r="K20" s="4">
-        <f>SUM(E20:I20)</f>
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="L20" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>50.4</v>
       </c>
       <c r="M20" s="4"/>
@@ -17681,11 +19318,11 @@
         <v>125</v>
       </c>
       <c r="K21" s="4">
-        <f>SUM(E21:I21)</f>
+        <f t="shared" si="0"/>
         <v>78.5</v>
       </c>
       <c r="L21" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>62.8</v>
       </c>
       <c r="M21" s="4"/>
@@ -17720,11 +19357,11 @@
         <v>125</v>
       </c>
       <c r="K22" s="4">
-        <f>SUM(E22:I22)</f>
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="L22" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>38.4</v>
       </c>
       <c r="M22" s="4"/>
@@ -17759,11 +19396,11 @@
         <v>125</v>
       </c>
       <c r="K23" s="4">
-        <f>SUM(E23:I23)</f>
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="L23" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>41.6</v>
       </c>
       <c r="M23" s="4"/>
@@ -17798,11 +19435,11 @@
         <v>125</v>
       </c>
       <c r="K24" s="4">
-        <f>SUM(E24:I24)</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="L24" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>39.200000000000003</v>
       </c>
       <c r="M24" s="4"/>
@@ -17837,11 +19474,11 @@
         <v>125</v>
       </c>
       <c r="K25" s="4">
-        <f>SUM(E25:I25)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="L25" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10.4</v>
       </c>
       <c r="M25" s="4"/>
@@ -17876,11 +19513,11 @@
         <v>125</v>
       </c>
       <c r="K26" s="4">
-        <f>SUM(E26:I26)</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="L26" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>22.400000000000002</v>
       </c>
       <c r="M26" s="4"/>
@@ -17915,11 +19552,11 @@
         <v>125</v>
       </c>
       <c r="K27" s="4">
-        <f>SUM(E27:I27)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="L27" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.1999999999999993</v>
       </c>
       <c r="M27" s="4"/>
@@ -17954,11 +19591,11 @@
         <v>125</v>
       </c>
       <c r="K28" s="4">
-        <f>SUM(E28:I28)</f>
+        <f t="shared" si="0"/>
         <v>66</v>
       </c>
       <c r="L28" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>52.800000000000004</v>
       </c>
       <c r="M28" s="4"/>
@@ -17993,11 +19630,11 @@
         <v>125</v>
       </c>
       <c r="K29" s="4">
-        <f>SUM(E29:I29)</f>
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="L29" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>40.799999999999997</v>
       </c>
       <c r="M29" s="4"/>
@@ -18032,11 +19669,11 @@
         <v>125</v>
       </c>
       <c r="K30" s="4">
-        <f>SUM(E30:I30)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L30" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M30" s="4"/>
@@ -18071,11 +19708,11 @@
         <v>125</v>
       </c>
       <c r="K31" s="4">
-        <f>SUM(E31:I31)</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="L31" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="M31" s="4"/>
@@ -18110,11 +19747,11 @@
         <v>125</v>
       </c>
       <c r="K32" s="4">
-        <f>SUM(E32:I32)</f>
+        <f t="shared" si="0"/>
         <v>73</v>
       </c>
       <c r="L32" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>58.4</v>
       </c>
       <c r="M32" s="4"/>
@@ -18149,11 +19786,11 @@
         <v>125</v>
       </c>
       <c r="K33" s="4">
-        <f>SUM(E33:I33)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="L33" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.6</v>
       </c>
       <c r="M33" s="4"/>
@@ -18188,11 +19825,11 @@
         <v>125</v>
       </c>
       <c r="K34" s="4">
-        <f>SUM(E34:I34)</f>
+        <f t="shared" si="0"/>
         <v>76</v>
       </c>
       <c r="L34" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>60.8</v>
       </c>
       <c r="M34" s="4"/>
@@ -18227,11 +19864,11 @@
         <v>125</v>
       </c>
       <c r="K35" s="4">
-        <f>SUM(E35:I35)</f>
+        <f t="shared" si="0"/>
         <v>89.5</v>
       </c>
       <c r="L35" s="8">
-        <f t="shared" ref="L35" si="1">K35/J35*100</f>
+        <f t="shared" ref="L35" si="2">K35/J35*100</f>
         <v>71.599999999999994</v>
       </c>
       <c r="M35" s="4"/>
@@ -18266,11 +19903,11 @@
         <v>125</v>
       </c>
       <c r="K36" s="4">
-        <f t="shared" ref="K36:K50" si="2">SUM(E36:I36)</f>
+        <f t="shared" ref="K36:K50" si="3">SUM(E36:I36)</f>
         <v>89</v>
       </c>
       <c r="L36" s="8">
-        <f t="shared" ref="L36:L50" si="3">K36/J36*100</f>
+        <f t="shared" ref="L36:L50" si="4">K36/J36*100</f>
         <v>71.2</v>
       </c>
       <c r="M36" s="4"/>
@@ -18305,11 +19942,11 @@
         <v>125</v>
       </c>
       <c r="K37" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>87</v>
       </c>
       <c r="L37" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>69.599999999999994</v>
       </c>
       <c r="M37" s="4"/>
@@ -18344,11 +19981,11 @@
         <v>125</v>
       </c>
       <c r="K38" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>74</v>
       </c>
       <c r="L38" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>59.199999999999996</v>
       </c>
       <c r="M38" s="4"/>
@@ -18383,11 +20020,11 @@
         <v>125</v>
       </c>
       <c r="K39" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>44</v>
       </c>
       <c r="L39" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>35.199999999999996</v>
       </c>
       <c r="M39" s="4"/>
@@ -18422,11 +20059,11 @@
         <v>125</v>
       </c>
       <c r="K40" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>71</v>
       </c>
       <c r="L40" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>56.8</v>
       </c>
       <c r="M40" s="4"/>
@@ -18461,11 +20098,11 @@
         <v>125</v>
       </c>
       <c r="K41" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>69</v>
       </c>
       <c r="L41" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>55.2</v>
       </c>
       <c r="M41" s="4"/>
@@ -18500,11 +20137,11 @@
         <v>125</v>
       </c>
       <c r="K42" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>78.5</v>
       </c>
       <c r="L42" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>62.8</v>
       </c>
       <c r="M42" s="4"/>
@@ -18539,11 +20176,11 @@
         <v>125</v>
       </c>
       <c r="K43" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="L43" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>20.8</v>
       </c>
       <c r="M43" s="4"/>
@@ -18578,11 +20215,11 @@
         <v>125</v>
       </c>
       <c r="K44" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="L44" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>24.8</v>
       </c>
       <c r="M44" s="4"/>
@@ -18617,11 +20254,11 @@
         <v>125</v>
       </c>
       <c r="K45" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>66</v>
       </c>
       <c r="L45" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>52.800000000000004</v>
       </c>
       <c r="M45" s="4"/>
@@ -18656,11 +20293,11 @@
         <v>125</v>
       </c>
       <c r="K46" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>56</v>
       </c>
       <c r="L46" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>44.800000000000004</v>
       </c>
       <c r="M46" s="4"/>
@@ -18695,11 +20332,11 @@
         <v>125</v>
       </c>
       <c r="K47" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="L47" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="M47" s="4"/>
@@ -18734,11 +20371,11 @@
         <v>125</v>
       </c>
       <c r="K48" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>47</v>
       </c>
       <c r="L48" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>37.6</v>
       </c>
       <c r="M48" s="4"/>
@@ -18773,11 +20410,11 @@
         <v>125</v>
       </c>
       <c r="K49" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>35</v>
       </c>
       <c r="L49" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>28.000000000000004</v>
       </c>
       <c r="M49" s="4"/>
@@ -18812,11 +20449,11 @@
         <v>125</v>
       </c>
       <c r="K50" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>72</v>
       </c>
       <c r="L50" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>57.599999999999994</v>
       </c>
       <c r="M50" s="4"/>
@@ -18851,11 +20488,11 @@
         <v>125</v>
       </c>
       <c r="K51" s="4">
-        <f t="shared" ref="K51:K52" si="4">SUM(E51:I51)</f>
+        <f t="shared" ref="K51:K52" si="5">SUM(E51:I51)</f>
         <v>45</v>
       </c>
       <c r="L51" s="8">
-        <f t="shared" ref="L51:L52" si="5">K51/J51*100</f>
+        <f t="shared" ref="L51:L52" si="6">K51/J51*100</f>
         <v>36</v>
       </c>
       <c r="M51" s="4"/>
@@ -18890,11 +20527,11 @@
         <v>125</v>
       </c>
       <c r="K52" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L52" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="M52" s="4"/>
@@ -18929,74 +20566,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="36" t="s">
+      <c r="C3" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="32" t="s">
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="32" t="s">
+      <c r="J3" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="32" t="s">
+      <c r="K3" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="32" t="s">
+      <c r="L3" s="34" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="35.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="34"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="36"/>
       <c r="E4" s="2" t="s">
         <v>120</v>
       </c>
@@ -19009,16 +20646,16 @@
       <c r="H4" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="32"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="35"/>
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="37"/>
       <c r="E5" s="3">
         <v>25</v>
       </c>
@@ -19035,9 +20672,9 @@
         <f>SUM(E5:H5)</f>
         <v>100</v>
       </c>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="32"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34"/>
     </row>
     <row r="6" spans="1:12" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
@@ -19066,7 +20703,7 @@
         <v>125</v>
       </c>
       <c r="J6" s="4">
-        <f>SUM(E6:H6)</f>
+        <f t="shared" ref="J6:J28" si="0">SUM(E6:H6)</f>
         <v>35</v>
       </c>
       <c r="K6" s="8">
@@ -19102,11 +20739,11 @@
         <v>125</v>
       </c>
       <c r="J7" s="4">
-        <f>SUM(E7:H7)</f>
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="K7" s="8">
-        <f t="shared" ref="K7:K28" si="0">J7/I7*100</f>
+        <f t="shared" ref="K7:K28" si="1">J7/I7*100</f>
         <v>46.400000000000006</v>
       </c>
       <c r="L7" s="4"/>
@@ -19138,11 +20775,11 @@
         <v>125</v>
       </c>
       <c r="J8" s="4">
-        <f>SUM(E8:H8)</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="K8" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="L8" s="4"/>
@@ -19174,11 +20811,11 @@
         <v>125</v>
       </c>
       <c r="J9" s="4">
-        <f>SUM(E9:H9)</f>
+        <f t="shared" si="0"/>
         <v>95</v>
       </c>
       <c r="K9" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>76</v>
       </c>
       <c r="L9" s="4"/>
@@ -19210,11 +20847,11 @@
         <v>125</v>
       </c>
       <c r="J10" s="4">
-        <f>SUM(E10:H10)</f>
+        <f t="shared" si="0"/>
         <v>77</v>
       </c>
       <c r="K10" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>61.6</v>
       </c>
       <c r="L10" s="4"/>
@@ -19246,11 +20883,11 @@
         <v>125</v>
       </c>
       <c r="J11" s="4">
-        <f>SUM(E11:H11)</f>
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="K11" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>51.2</v>
       </c>
       <c r="L11" s="4"/>
@@ -19282,11 +20919,11 @@
         <v>125</v>
       </c>
       <c r="J12" s="4">
-        <f>SUM(E12:H12)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="K12" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="L12" s="4"/>
@@ -19318,11 +20955,11 @@
         <v>125</v>
       </c>
       <c r="J13" s="4">
-        <f>SUM(E13:H13)</f>
+        <f t="shared" si="0"/>
         <v>71</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>56.8</v>
       </c>
       <c r="L13" s="4"/>
@@ -19354,11 +20991,11 @@
         <v>125</v>
       </c>
       <c r="J14" s="4">
-        <f>SUM(E14:H14)</f>
+        <f t="shared" si="0"/>
         <v>87</v>
       </c>
       <c r="K14" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>69.599999999999994</v>
       </c>
       <c r="L14" s="4"/>
@@ -19390,11 +21027,11 @@
         <v>125</v>
       </c>
       <c r="J15" s="4">
-        <f>SUM(E15:H15)</f>
+        <f t="shared" si="0"/>
         <v>67</v>
       </c>
       <c r="K15" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>53.6</v>
       </c>
       <c r="L15" s="4"/>
@@ -19426,11 +21063,11 @@
         <v>125</v>
       </c>
       <c r="J16" s="4">
-        <f>SUM(E16:H16)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="K16" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20.8</v>
       </c>
       <c r="L16" s="4"/>
@@ -19462,11 +21099,11 @@
         <v>125</v>
       </c>
       <c r="J17" s="4">
-        <f>SUM(E17:H17)</f>
+        <f t="shared" si="0"/>
         <v>85</v>
       </c>
       <c r="K17" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>68</v>
       </c>
       <c r="L17" s="4"/>
@@ -19498,11 +21135,11 @@
         <v>125</v>
       </c>
       <c r="J18" s="4">
-        <f>SUM(E18:H18)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>28.000000000000004</v>
       </c>
       <c r="L18" s="4"/>
@@ -19534,11 +21171,11 @@
         <v>125</v>
       </c>
       <c r="J19" s="4">
-        <f>SUM(E19:H19)</f>
+        <f t="shared" si="0"/>
         <v>81</v>
       </c>
       <c r="K19" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>64.8</v>
       </c>
       <c r="L19" s="4"/>
@@ -19570,11 +21207,11 @@
         <v>125</v>
       </c>
       <c r="J20" s="4">
-        <f>SUM(E20:H20)</f>
+        <f t="shared" si="0"/>
         <v>93</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>74.400000000000006</v>
       </c>
       <c r="L20" s="4"/>
@@ -19606,11 +21243,11 @@
         <v>125</v>
       </c>
       <c r="J21" s="4">
-        <f>SUM(E21:H21)</f>
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>51.2</v>
       </c>
       <c r="L21" s="4"/>
@@ -19642,11 +21279,11 @@
         <v>125</v>
       </c>
       <c r="J22" s="4">
-        <f>SUM(E22:H22)</f>
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="K22" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>32.800000000000004</v>
       </c>
       <c r="L22" s="4"/>
@@ -19678,11 +21315,11 @@
         <v>125</v>
       </c>
       <c r="J23" s="4">
-        <f>SUM(E23:H23)</f>
+        <f t="shared" si="0"/>
         <v>87</v>
       </c>
       <c r="K23" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>69.599999999999994</v>
       </c>
       <c r="L23" s="4"/>
@@ -19714,11 +21351,11 @@
         <v>125</v>
       </c>
       <c r="J24" s="4">
-        <f>SUM(E24:H24)</f>
+        <f t="shared" si="0"/>
         <v>89</v>
       </c>
       <c r="K24" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>71.2</v>
       </c>
       <c r="L24" s="4"/>
@@ -19750,11 +21387,11 @@
         <v>125</v>
       </c>
       <c r="J25" s="4">
-        <f>SUM(E25:H25)</f>
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30.4</v>
       </c>
       <c r="L25" s="4"/>
@@ -19786,11 +21423,11 @@
         <v>125</v>
       </c>
       <c r="J26" s="4">
-        <f>SUM(E26:H26)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="K26" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>26.400000000000002</v>
       </c>
       <c r="L26" s="4"/>
@@ -19822,11 +21459,11 @@
         <v>125</v>
       </c>
       <c r="J27" s="4">
-        <f>SUM(E27:H27)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="L27" s="4"/>
@@ -19858,11 +21495,11 @@
         <v>125</v>
       </c>
       <c r="J28" s="4">
-        <f>SUM(E28:H28)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K28" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L28" s="4"/>
@@ -19898,83 +21535,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="36" t="s">
+      <c r="C3" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="32" t="s">
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="32" t="s">
+      <c r="M3" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="32" t="s">
+      <c r="N3" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="32" t="s">
+      <c r="O3" s="34" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="34"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="36"/>
       <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
@@ -19996,16 +21633,16 @@
       <c r="K4" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="32"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="35"/>
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="37"/>
       <c r="E5" s="3">
         <v>25</v>
       </c>
@@ -20031,9 +21668,9 @@
         <f>SUM(E5:K5)</f>
         <v>175</v>
       </c>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="32"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="34"/>
     </row>
     <row r="6" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">

--- a/Sindhi Muslim/Result Sheet/Monthly Test - Oct 2024.xlsx
+++ b/Sindhi Muslim/Result Sheet/Monthly Test - Oct 2024.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Result Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009C673E-0509-41BA-9675-F426F632532A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE708CC-230E-44DF-8CE5-72808B3353FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{A3810461-FCAA-4427-95C3-213E25AAD5DA}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="601">
   <si>
     <t>GOVERNMENT HIGH SCHOOL SINDHI JAMAAT CO-OPERATIVE HOUSING SOCIETY</t>
   </si>
@@ -5933,7 +5933,7 @@
         <v>70</v>
       </c>
       <c r="Q8" s="4">
-        <f t="shared" ref="Q8:Q31" si="0">SUM(F8:O8)</f>
+        <f t="shared" ref="Q8:Q30" si="0">SUM(F8:O8)</f>
         <v>62</v>
       </c>
       <c r="R8" s="4">
@@ -9225,6 +9225,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
     <col min="6" max="15" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9345,25 +9347,26 @@
       <c r="D5" s="34"/>
       <c r="E5" s="37"/>
       <c r="F5" s="3">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="G5" s="3">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="H5" s="3">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="I5" s="3">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="J5" s="3">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>281</v>
       </c>
       <c r="L5" s="3">
-        <v>500</v>
+        <f>SUM(F5:J5)</f>
+        <v>25</v>
       </c>
       <c r="M5" s="34"/>
       <c r="N5" s="34"/>
@@ -9407,15 +9410,35 @@
       <c r="F7" s="4">
         <v>0</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
+      <c r="G7" s="4">
+        <v>4</v>
+      </c>
+      <c r="H7" s="4">
+        <v>5</v>
+      </c>
+      <c r="I7" s="4">
+        <v>4</v>
+      </c>
+      <c r="J7" s="4">
+        <v>4</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L7" s="4">
+        <v>25</v>
+      </c>
+      <c r="M7" s="4">
+        <f>SUM(F7:J7)</f>
+        <v>17</v>
+      </c>
+      <c r="N7" s="4">
+        <f>M7/L7*100</f>
+        <v>68</v>
+      </c>
+      <c r="O7" s="4">
+        <v>24</v>
+      </c>
       <c r="P7" s="4"/>
     </row>
     <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9432,16 +9455,38 @@
       <c r="E8" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
+      <c r="F8" s="4">
+        <v>2</v>
+      </c>
+      <c r="G8" s="4">
+        <v>4</v>
+      </c>
+      <c r="H8" s="4">
+        <v>5</v>
+      </c>
+      <c r="I8" s="4">
+        <v>5</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L8" s="4">
+        <v>25</v>
+      </c>
+      <c r="M8" s="4">
+        <f t="shared" ref="M8:M38" si="0">SUM(F8:J8)</f>
+        <v>16</v>
+      </c>
+      <c r="N8" s="4">
+        <f t="shared" ref="N8:N38" si="1">M8/L8*100</f>
+        <v>64</v>
+      </c>
+      <c r="O8" s="4">
+        <v>22</v>
+      </c>
       <c r="P8" s="4"/>
     </row>
     <row r="9" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9458,16 +9503,38 @@
       <c r="E9" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
+      <c r="F9" s="4">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4">
+        <v>5</v>
+      </c>
+      <c r="H9" s="4">
+        <v>1</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1</v>
+      </c>
+      <c r="J9" s="4">
+        <v>1</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L9" s="4">
+        <v>25</v>
+      </c>
+      <c r="M9" s="4">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="N9" s="4">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="O9" s="4">
+        <v>22</v>
+      </c>
       <c r="P9" s="4"/>
     </row>
     <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9484,16 +9551,38 @@
       <c r="E10" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
+      <c r="F10" s="4">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4">
+        <v>4</v>
+      </c>
+      <c r="H10" s="4">
+        <v>1</v>
+      </c>
+      <c r="I10" s="4">
+        <v>4</v>
+      </c>
+      <c r="J10" s="4">
+        <v>3</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L10" s="4">
+        <v>25</v>
+      </c>
+      <c r="M10" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="N10" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="O10" s="4">
+        <v>18</v>
+      </c>
       <c r="P10" s="4"/>
     </row>
     <row r="11" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9510,16 +9599,38 @@
       <c r="E11" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
+      <c r="F11" s="4">
+        <v>2</v>
+      </c>
+      <c r="G11" s="4">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4">
+        <v>1</v>
+      </c>
+      <c r="I11" s="4">
+        <v>2</v>
+      </c>
+      <c r="J11" s="4">
+        <v>1</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L11" s="4">
+        <v>25</v>
+      </c>
+      <c r="M11" s="4">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="N11" s="4">
+        <f t="shared" si="1"/>
+        <v>28.000000000000004</v>
+      </c>
+      <c r="O11" s="4">
+        <v>26</v>
+      </c>
       <c r="P11" s="4"/>
     </row>
     <row r="12" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9536,16 +9647,38 @@
       <c r="E12" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
+      <c r="F12" s="4">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <v>2</v>
+      </c>
+      <c r="H12" s="4">
+        <v>1</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L12" s="4">
+        <v>25</v>
+      </c>
+      <c r="M12" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="N12" s="4">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="O12" s="4">
+        <v>24</v>
+      </c>
       <c r="P12" s="4"/>
     </row>
     <row r="13" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9562,16 +9695,38 @@
       <c r="E13" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
+      <c r="F13" s="4">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <v>4</v>
+      </c>
+      <c r="H13" s="4">
+        <v>3</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L13" s="4">
+        <v>25</v>
+      </c>
+      <c r="M13" s="4">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="N13" s="4">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="O13" s="4">
+        <v>24</v>
+      </c>
       <c r="P13" s="4"/>
     </row>
     <row r="14" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9588,16 +9743,38 @@
       <c r="E14" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
+      <c r="F14" s="4">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4">
+        <v>4</v>
+      </c>
+      <c r="I14" s="4">
+        <v>4</v>
+      </c>
+      <c r="J14" s="4">
+        <v>3</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L14" s="4">
+        <v>25</v>
+      </c>
+      <c r="M14" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="N14" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="O14" s="4">
+        <v>23</v>
+      </c>
       <c r="P14" s="4"/>
     </row>
     <row r="15" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9614,16 +9791,38 @@
       <c r="E15" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <v>3</v>
+      </c>
+      <c r="H15" s="4">
+        <v>5</v>
+      </c>
+      <c r="I15" s="4">
+        <v>2</v>
+      </c>
+      <c r="J15" s="4">
+        <v>2</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L15" s="4">
+        <v>25</v>
+      </c>
+      <c r="M15" s="4">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="N15" s="4">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="O15" s="4">
+        <v>26</v>
+      </c>
       <c r="P15" s="4"/>
     </row>
     <row r="16" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9640,16 +9839,38 @@
       <c r="E16" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
+      <c r="F16" s="4">
+        <v>5</v>
+      </c>
+      <c r="G16" s="4">
+        <v>5</v>
+      </c>
+      <c r="H16" s="4">
+        <v>5</v>
+      </c>
+      <c r="I16" s="4">
+        <v>1</v>
+      </c>
+      <c r="J16" s="4">
+        <v>1</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L16" s="4">
+        <v>25</v>
+      </c>
+      <c r="M16" s="4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="N16" s="4">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+      <c r="O16" s="4">
+        <v>26</v>
+      </c>
       <c r="P16" s="4"/>
     </row>
     <row r="17" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9666,16 +9887,38 @@
       <c r="E17" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
+      <c r="F17" s="4">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4">
+        <v>3</v>
+      </c>
+      <c r="I17" s="4">
+        <v>4</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L17" s="4">
+        <v>25</v>
+      </c>
+      <c r="M17" s="4">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="N17" s="4">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="O17" s="4">
+        <v>20</v>
+      </c>
       <c r="P17" s="4"/>
     </row>
     <row r="18" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9692,16 +9935,38 @@
       <c r="E18" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
+      <c r="F18" s="4">
+        <v>4</v>
+      </c>
+      <c r="G18" s="4">
+        <v>3</v>
+      </c>
+      <c r="H18" s="4">
+        <v>4</v>
+      </c>
+      <c r="I18" s="4">
+        <v>1</v>
+      </c>
+      <c r="J18" s="4">
+        <v>1</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L18" s="4">
+        <v>25</v>
+      </c>
+      <c r="M18" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="N18" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="O18" s="4">
+        <v>24</v>
+      </c>
       <c r="P18" s="4"/>
     </row>
     <row r="19" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9718,16 +9983,38 @@
       <c r="E19" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
+      <c r="F19" s="4">
+        <v>2</v>
+      </c>
+      <c r="G19" s="4">
+        <v>3</v>
+      </c>
+      <c r="H19" s="4">
+        <v>5</v>
+      </c>
+      <c r="I19" s="4">
+        <v>2</v>
+      </c>
+      <c r="J19" s="4">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L19" s="4">
+        <v>25</v>
+      </c>
+      <c r="M19" s="4">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="N19" s="4">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="O19" s="4">
+        <v>25</v>
+      </c>
       <c r="P19" s="4"/>
     </row>
     <row r="20" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9744,16 +10031,38 @@
       <c r="E20" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
+      <c r="F20" s="4">
+        <v>4</v>
+      </c>
+      <c r="G20" s="4">
+        <v>5</v>
+      </c>
+      <c r="H20" s="4">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4">
+        <v>4</v>
+      </c>
+      <c r="J20" s="4">
+        <v>4</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L20" s="4">
+        <v>25</v>
+      </c>
+      <c r="M20" s="4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="N20" s="4">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+      <c r="O20" s="4">
+        <v>26</v>
+      </c>
       <c r="P20" s="4"/>
     </row>
     <row r="21" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9770,16 +10079,38 @@
       <c r="E21" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
+      <c r="F21" s="4">
+        <v>4</v>
+      </c>
+      <c r="G21" s="4">
+        <v>5</v>
+      </c>
+      <c r="H21" s="4">
+        <v>2</v>
+      </c>
+      <c r="I21" s="4">
+        <v>4</v>
+      </c>
+      <c r="J21" s="4">
+        <v>5</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L21" s="4">
+        <v>25</v>
+      </c>
+      <c r="M21" s="4">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="N21" s="4">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="O21" s="4">
+        <v>27</v>
+      </c>
       <c r="P21" s="4"/>
     </row>
     <row r="22" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9796,16 +10127,38 @@
       <c r="E22" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
+      <c r="F22" s="4">
+        <v>3</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <v>5</v>
+      </c>
+      <c r="I22" s="4">
+        <v>2</v>
+      </c>
+      <c r="J22" s="4">
+        <v>0</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L22" s="4">
+        <v>25</v>
+      </c>
+      <c r="M22" s="4">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N22" s="4">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="O22" s="4">
+        <v>22</v>
+      </c>
       <c r="P22" s="4"/>
     </row>
     <row r="23" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9822,16 +10175,38 @@
       <c r="E23" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
+      <c r="F23" s="4">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <v>1</v>
+      </c>
+      <c r="H23" s="4">
+        <v>4</v>
+      </c>
+      <c r="I23" s="4">
+        <v>3</v>
+      </c>
+      <c r="J23" s="4">
+        <v>0</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L23" s="4">
+        <v>25</v>
+      </c>
+      <c r="M23" s="4">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="N23" s="4">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="O23" s="4">
+        <v>21</v>
+      </c>
       <c r="P23" s="4"/>
     </row>
     <row r="24" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9848,16 +10223,38 @@
       <c r="E24" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
+      <c r="F24" s="4">
+        <v>1</v>
+      </c>
+      <c r="G24" s="4">
+        <v>2</v>
+      </c>
+      <c r="H24" s="4">
+        <v>0</v>
+      </c>
+      <c r="I24" s="4">
+        <v>0</v>
+      </c>
+      <c r="J24" s="4">
+        <v>0</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L24" s="4">
+        <v>25</v>
+      </c>
+      <c r="M24" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="N24" s="4">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="O24" s="4">
+        <v>26</v>
+      </c>
       <c r="P24" s="4"/>
     </row>
     <row r="25" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9874,16 +10271,38 @@
       <c r="E25" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="4"/>
+      <c r="F25" s="4">
+        <v>1</v>
+      </c>
+      <c r="G25" s="4">
+        <v>3</v>
+      </c>
+      <c r="H25" s="4">
+        <v>2</v>
+      </c>
+      <c r="I25" s="4">
+        <v>1</v>
+      </c>
+      <c r="J25" s="4">
+        <v>0</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L25" s="4">
+        <v>25</v>
+      </c>
+      <c r="M25" s="4">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="N25" s="4">
+        <f t="shared" si="1"/>
+        <v>28.000000000000004</v>
+      </c>
+      <c r="O25" s="4">
+        <v>26</v>
+      </c>
       <c r="P25" s="4"/>
     </row>
     <row r="26" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9900,16 +10319,38 @@
       <c r="E26" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
-      <c r="O26" s="4"/>
+      <c r="F26" s="4">
+        <v>1</v>
+      </c>
+      <c r="G26" s="4">
+        <v>5</v>
+      </c>
+      <c r="H26" s="4">
+        <v>1</v>
+      </c>
+      <c r="I26" s="4">
+        <v>1</v>
+      </c>
+      <c r="J26" s="4">
+        <v>1</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L26" s="4">
+        <v>25</v>
+      </c>
+      <c r="M26" s="4">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="N26" s="4">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="O26" s="4">
+        <v>26</v>
+      </c>
       <c r="P26" s="4"/>
     </row>
     <row r="27" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9926,16 +10367,38 @@
       <c r="E27" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4"/>
+      <c r="F27" s="4">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4">
+        <v>1</v>
+      </c>
+      <c r="I27" s="4">
+        <v>2</v>
+      </c>
+      <c r="J27" s="4">
+        <v>0</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L27" s="4">
+        <v>25</v>
+      </c>
+      <c r="M27" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="N27" s="4">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="O27" s="4">
+        <v>24</v>
+      </c>
       <c r="P27" s="4"/>
     </row>
     <row r="28" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9952,16 +10415,38 @@
       <c r="E28" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
+      <c r="F28" s="4">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4">
+        <v>4</v>
+      </c>
+      <c r="H28" s="4">
+        <v>3</v>
+      </c>
+      <c r="I28" s="4">
+        <v>1</v>
+      </c>
+      <c r="J28" s="4">
+        <v>1</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L28" s="4">
+        <v>25</v>
+      </c>
+      <c r="M28" s="4">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="N28" s="4">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="O28" s="4">
+        <v>26</v>
+      </c>
       <c r="P28" s="4"/>
     </row>
     <row r="29" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9978,16 +10463,38 @@
       <c r="E29" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="4"/>
+      <c r="F29" s="4">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4">
+        <v>1</v>
+      </c>
+      <c r="H29" s="4">
+        <v>2</v>
+      </c>
+      <c r="I29" s="4">
+        <v>1</v>
+      </c>
+      <c r="J29" s="4">
+        <v>3</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L29" s="4">
+        <v>25</v>
+      </c>
+      <c r="M29" s="4">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="N29" s="4">
+        <f t="shared" si="1"/>
+        <v>28.000000000000004</v>
+      </c>
+      <c r="O29" s="4">
+        <v>18</v>
+      </c>
       <c r="P29" s="4"/>
     </row>
     <row r="30" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10004,16 +10511,38 @@
       <c r="E30" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
+      <c r="F30" s="4">
+        <v>2</v>
+      </c>
+      <c r="G30" s="4">
+        <v>4</v>
+      </c>
+      <c r="H30" s="4">
+        <v>5</v>
+      </c>
+      <c r="I30" s="4">
+        <v>2</v>
+      </c>
+      <c r="J30" s="4">
+        <v>0</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L30" s="4">
+        <v>25</v>
+      </c>
+      <c r="M30" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="N30" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="O30" s="4">
+        <v>20</v>
+      </c>
       <c r="P30" s="4"/>
     </row>
     <row r="31" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10030,16 +10559,38 @@
       <c r="E31" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
+      <c r="F31" s="4">
+        <v>2</v>
+      </c>
+      <c r="G31" s="4">
+        <v>1</v>
+      </c>
+      <c r="H31" s="4">
+        <v>1</v>
+      </c>
+      <c r="I31" s="4">
+        <v>2</v>
+      </c>
+      <c r="J31" s="4">
+        <v>1</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L31" s="4">
+        <v>25</v>
+      </c>
+      <c r="M31" s="4">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="N31" s="4">
+        <f t="shared" si="1"/>
+        <v>28.000000000000004</v>
+      </c>
+      <c r="O31" s="4">
+        <v>22</v>
+      </c>
       <c r="P31" s="4"/>
     </row>
     <row r="32" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10056,16 +10607,38 @@
       <c r="E32" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
+      <c r="F32" s="4">
+        <v>0</v>
+      </c>
+      <c r="G32" s="4">
+        <v>3</v>
+      </c>
+      <c r="H32" s="4">
+        <v>5</v>
+      </c>
+      <c r="I32" s="4">
+        <v>2</v>
+      </c>
+      <c r="J32" s="4">
+        <v>2</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L32" s="4">
+        <v>25</v>
+      </c>
+      <c r="M32" s="4">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="N32" s="4">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="O32" s="4">
+        <v>16</v>
+      </c>
       <c r="P32" s="4"/>
     </row>
     <row r="33" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10082,16 +10655,38 @@
       <c r="E33" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
+      <c r="F33" s="4">
+        <v>1</v>
+      </c>
+      <c r="G33" s="4">
+        <v>4</v>
+      </c>
+      <c r="H33" s="4">
+        <v>4</v>
+      </c>
+      <c r="I33" s="4">
+        <v>3</v>
+      </c>
+      <c r="J33" s="4">
+        <v>1</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L33" s="4">
+        <v>25</v>
+      </c>
+      <c r="M33" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="N33" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="O33" s="4">
+        <v>26</v>
+      </c>
       <c r="P33" s="4"/>
     </row>
     <row r="34" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10108,16 +10703,38 @@
       <c r="E34" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
+      <c r="F34" s="4">
+        <v>0</v>
+      </c>
+      <c r="G34" s="4">
+        <v>1</v>
+      </c>
+      <c r="H34" s="4">
+        <v>2</v>
+      </c>
+      <c r="I34" s="4">
+        <v>1</v>
+      </c>
+      <c r="J34" s="4">
+        <v>3</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L34" s="4">
+        <v>25</v>
+      </c>
+      <c r="M34" s="4">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="N34" s="4">
+        <f t="shared" si="1"/>
+        <v>28.000000000000004</v>
+      </c>
+      <c r="O34" s="4">
+        <v>20</v>
+      </c>
       <c r="P34" s="4"/>
     </row>
     <row r="35" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10134,16 +10751,38 @@
       <c r="E35" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
+      <c r="F35" s="4">
+        <v>2</v>
+      </c>
+      <c r="G35" s="4">
+        <v>5</v>
+      </c>
+      <c r="H35" s="4">
+        <v>5</v>
+      </c>
+      <c r="I35" s="4">
+        <v>4</v>
+      </c>
+      <c r="J35" s="4">
+        <v>4</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L35" s="4">
+        <v>25</v>
+      </c>
+      <c r="M35" s="4">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="N35" s="4">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="O35" s="4">
+        <v>25</v>
+      </c>
       <c r="P35" s="4"/>
     </row>
     <row r="36" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10160,16 +10799,38 @@
       <c r="E36" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
+      <c r="F36" s="4">
+        <v>2</v>
+      </c>
+      <c r="G36" s="4">
+        <v>4</v>
+      </c>
+      <c r="H36" s="4">
+        <v>5</v>
+      </c>
+      <c r="I36" s="4">
+        <v>1</v>
+      </c>
+      <c r="J36" s="4">
+        <v>1</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L36" s="4">
+        <v>25</v>
+      </c>
+      <c r="M36" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="N36" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="O36" s="4">
+        <v>25</v>
+      </c>
       <c r="P36" s="4"/>
     </row>
     <row r="37" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10186,16 +10847,38 @@
       <c r="E37" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
+      <c r="F37" s="4">
+        <v>2</v>
+      </c>
+      <c r="G37" s="4">
+        <v>5</v>
+      </c>
+      <c r="H37" s="4">
+        <v>4</v>
+      </c>
+      <c r="I37" s="4">
+        <v>2</v>
+      </c>
+      <c r="J37" s="4">
+        <v>0</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L37" s="4">
+        <v>25</v>
+      </c>
+      <c r="M37" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="N37" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="O37" s="4">
+        <v>19</v>
+      </c>
       <c r="P37" s="4"/>
     </row>
     <row r="38" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10212,16 +10895,38 @@
       <c r="E38" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
+      <c r="F38" s="4">
+        <v>0</v>
+      </c>
+      <c r="G38" s="4">
+        <v>3</v>
+      </c>
+      <c r="H38" s="4">
+        <v>5</v>
+      </c>
+      <c r="I38" s="4">
+        <v>2</v>
+      </c>
+      <c r="J38" s="4">
+        <v>0</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L38" s="4">
+        <v>25</v>
+      </c>
+      <c r="M38" s="4">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="N38" s="4">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="O38" s="4">
+        <v>23</v>
+      </c>
       <c r="P38" s="4"/>
     </row>
     <row r="39" spans="1:16" ht="21" x14ac:dyDescent="0.35">
@@ -10258,16 +10963,38 @@
       <c r="E40" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="4"/>
+      <c r="F40" s="4">
+        <v>2</v>
+      </c>
+      <c r="G40" s="4">
+        <v>4</v>
+      </c>
+      <c r="H40" s="4">
+        <v>5</v>
+      </c>
+      <c r="I40" s="4">
+        <v>2</v>
+      </c>
+      <c r="J40" s="4">
+        <v>0</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L40" s="4">
+        <v>25</v>
+      </c>
+      <c r="M40" s="4">
+        <f>SUM(F40:J40)</f>
+        <v>13</v>
+      </c>
+      <c r="N40" s="4">
+        <f>M40/L40*100</f>
+        <v>52</v>
+      </c>
+      <c r="O40" s="4">
+        <v>26</v>
+      </c>
       <c r="P40" s="4"/>
     </row>
     <row r="41" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10284,16 +11011,38 @@
       <c r="E41" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4"/>
+      <c r="F41" s="4">
+        <v>1</v>
+      </c>
+      <c r="G41" s="4">
+        <v>5</v>
+      </c>
+      <c r="H41" s="4">
+        <v>1</v>
+      </c>
+      <c r="I41" s="4">
+        <v>1</v>
+      </c>
+      <c r="J41" s="4">
+        <v>1</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L41" s="4">
+        <v>25</v>
+      </c>
+      <c r="M41" s="4">
+        <f t="shared" ref="M41:M63" si="2">SUM(F41:J41)</f>
+        <v>9</v>
+      </c>
+      <c r="N41" s="4">
+        <f t="shared" ref="N41:N63" si="3">M41/L41*100</f>
+        <v>36</v>
+      </c>
+      <c r="O41" s="4">
+        <v>16</v>
+      </c>
       <c r="P41" s="4"/>
     </row>
     <row r="42" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10310,16 +11059,38 @@
       <c r="E42" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4"/>
+      <c r="F42" s="4">
+        <v>2</v>
+      </c>
+      <c r="G42" s="4">
+        <v>5</v>
+      </c>
+      <c r="H42" s="4">
+        <v>5</v>
+      </c>
+      <c r="I42" s="4">
+        <v>4</v>
+      </c>
+      <c r="J42" s="4">
+        <v>4</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L42" s="4">
+        <v>25</v>
+      </c>
+      <c r="M42" s="4">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="N42" s="4">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="O42" s="4">
+        <v>26</v>
+      </c>
       <c r="P42" s="4"/>
     </row>
     <row r="43" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10336,16 +11107,38 @@
       <c r="E43" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="4"/>
-      <c r="M43" s="4"/>
-      <c r="N43" s="4"/>
-      <c r="O43" s="4"/>
+      <c r="F43" s="4">
+        <v>5</v>
+      </c>
+      <c r="G43" s="4">
+        <v>5</v>
+      </c>
+      <c r="H43" s="4">
+        <v>1</v>
+      </c>
+      <c r="I43" s="4">
+        <v>5</v>
+      </c>
+      <c r="J43" s="4">
+        <v>1</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L43" s="4">
+        <v>25</v>
+      </c>
+      <c r="M43" s="4">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="N43" s="4">
+        <f t="shared" si="3"/>
+        <v>68</v>
+      </c>
+      <c r="O43" s="4">
+        <v>21</v>
+      </c>
       <c r="P43" s="4"/>
     </row>
     <row r="44" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10362,16 +11155,38 @@
       <c r="E44" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
-      <c r="M44" s="4"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4"/>
+      <c r="F44" s="4">
+        <v>2</v>
+      </c>
+      <c r="G44" s="4">
+        <v>5</v>
+      </c>
+      <c r="H44" s="4">
+        <v>5</v>
+      </c>
+      <c r="I44" s="4">
+        <v>4</v>
+      </c>
+      <c r="J44" s="4">
+        <v>4</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L44" s="4">
+        <v>25</v>
+      </c>
+      <c r="M44" s="4">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="N44" s="4">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="O44" s="4">
+        <v>26</v>
+      </c>
       <c r="P44" s="4"/>
     </row>
     <row r="45" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10388,16 +11203,38 @@
       <c r="E45" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="4"/>
-      <c r="L45" s="4"/>
-      <c r="M45" s="4"/>
-      <c r="N45" s="4"/>
-      <c r="O45" s="4"/>
+      <c r="F45" s="4">
+        <v>5</v>
+      </c>
+      <c r="G45" s="4">
+        <v>4</v>
+      </c>
+      <c r="H45" s="4">
+        <v>5</v>
+      </c>
+      <c r="I45" s="4">
+        <v>1</v>
+      </c>
+      <c r="J45" s="4">
+        <v>1</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L45" s="4">
+        <v>25</v>
+      </c>
+      <c r="M45" s="4">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="N45" s="4">
+        <f t="shared" si="3"/>
+        <v>64</v>
+      </c>
+      <c r="O45" s="4">
+        <v>21</v>
+      </c>
       <c r="P45" s="4"/>
     </row>
     <row r="46" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10414,16 +11251,38 @@
       <c r="E46" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="4"/>
-      <c r="L46" s="4"/>
-      <c r="M46" s="4"/>
-      <c r="N46" s="4"/>
-      <c r="O46" s="4"/>
+      <c r="F46" s="4">
+        <v>1</v>
+      </c>
+      <c r="G46" s="4">
+        <v>5</v>
+      </c>
+      <c r="H46" s="4">
+        <v>3</v>
+      </c>
+      <c r="I46" s="4">
+        <v>1</v>
+      </c>
+      <c r="J46" s="4">
+        <v>1</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L46" s="4">
+        <v>25</v>
+      </c>
+      <c r="M46" s="4">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="N46" s="4">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="O46" s="4">
+        <v>25</v>
+      </c>
       <c r="P46" s="4"/>
     </row>
     <row r="47" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10440,16 +11299,38 @@
       <c r="E47" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
-      <c r="M47" s="4"/>
-      <c r="N47" s="4"/>
-      <c r="O47" s="4"/>
+      <c r="F47" s="4">
+        <v>1</v>
+      </c>
+      <c r="G47" s="4">
+        <v>4</v>
+      </c>
+      <c r="H47" s="4">
+        <v>5</v>
+      </c>
+      <c r="I47" s="4">
+        <v>3</v>
+      </c>
+      <c r="J47" s="4">
+        <v>4</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L47" s="4">
+        <v>25</v>
+      </c>
+      <c r="M47" s="4">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="N47" s="4">
+        <f t="shared" si="3"/>
+        <v>68</v>
+      </c>
+      <c r="O47" s="4">
+        <v>25</v>
+      </c>
       <c r="P47" s="4"/>
     </row>
     <row r="48" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10466,16 +11347,38 @@
       <c r="E48" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
-      <c r="N48" s="4"/>
-      <c r="O48" s="4"/>
+      <c r="F48" s="4">
+        <v>1</v>
+      </c>
+      <c r="G48" s="4">
+        <v>5</v>
+      </c>
+      <c r="H48" s="4">
+        <v>5</v>
+      </c>
+      <c r="I48" s="4">
+        <v>0</v>
+      </c>
+      <c r="J48" s="4">
+        <v>0</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L48" s="4">
+        <v>25</v>
+      </c>
+      <c r="M48" s="4">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="N48" s="4">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="O48" s="4">
+        <v>25</v>
+      </c>
       <c r="P48" s="4"/>
     </row>
     <row r="49" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10492,16 +11395,38 @@
       <c r="E49" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
-      <c r="M49" s="4"/>
-      <c r="N49" s="4"/>
-      <c r="O49" s="4"/>
+      <c r="F49" s="4">
+        <v>1</v>
+      </c>
+      <c r="G49" s="4">
+        <v>4</v>
+      </c>
+      <c r="H49" s="4">
+        <v>5</v>
+      </c>
+      <c r="I49" s="4">
+        <v>3</v>
+      </c>
+      <c r="J49" s="4">
+        <v>4</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L49" s="4">
+        <v>25</v>
+      </c>
+      <c r="M49" s="4">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="N49" s="4">
+        <f t="shared" si="3"/>
+        <v>68</v>
+      </c>
+      <c r="O49" s="4">
+        <v>26</v>
+      </c>
       <c r="P49" s="4"/>
     </row>
     <row r="50" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10518,16 +11443,38 @@
       <c r="E50" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4"/>
-      <c r="N50" s="4"/>
-      <c r="O50" s="4"/>
+      <c r="F50" s="4">
+        <v>4</v>
+      </c>
+      <c r="G50" s="4">
+        <v>0</v>
+      </c>
+      <c r="H50" s="4">
+        <v>4</v>
+      </c>
+      <c r="I50" s="4">
+        <v>2</v>
+      </c>
+      <c r="J50" s="4">
+        <v>1</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L50" s="4">
+        <v>25</v>
+      </c>
+      <c r="M50" s="4">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="N50" s="4">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="O50" s="4">
+        <v>11</v>
+      </c>
       <c r="P50" s="4"/>
     </row>
     <row r="51" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10544,16 +11491,38 @@
       <c r="E51" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
+      <c r="F51" s="4">
+        <v>4</v>
+      </c>
+      <c r="G51" s="4">
+        <v>0</v>
+      </c>
+      <c r="H51" s="4">
+        <v>5</v>
+      </c>
+      <c r="I51" s="4">
+        <v>3</v>
+      </c>
+      <c r="J51" s="4">
+        <v>1</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L51" s="4">
+        <v>25</v>
+      </c>
+      <c r="M51" s="4">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="N51" s="4">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="O51" s="4">
+        <v>21</v>
+      </c>
       <c r="P51" s="4"/>
     </row>
     <row r="52" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10570,16 +11539,38 @@
       <c r="E52" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
-      <c r="O52" s="4"/>
+      <c r="F52" s="4">
+        <v>5</v>
+      </c>
+      <c r="G52" s="4">
+        <v>4</v>
+      </c>
+      <c r="H52" s="4">
+        <v>5</v>
+      </c>
+      <c r="I52" s="4">
+        <v>1</v>
+      </c>
+      <c r="J52" s="4">
+        <v>1</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L52" s="4">
+        <v>25</v>
+      </c>
+      <c r="M52" s="4">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="N52" s="4">
+        <f t="shared" si="3"/>
+        <v>64</v>
+      </c>
+      <c r="O52" s="4">
+        <v>14</v>
+      </c>
       <c r="P52" s="4"/>
     </row>
     <row r="53" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10596,16 +11587,38 @@
       <c r="E53" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
+      <c r="F53" s="4">
+        <v>3</v>
+      </c>
+      <c r="G53" s="4">
+        <v>0</v>
+      </c>
+      <c r="H53" s="4">
+        <v>4</v>
+      </c>
+      <c r="I53" s="4">
+        <v>0</v>
+      </c>
+      <c r="J53" s="4">
+        <v>1</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L53" s="4">
+        <v>25</v>
+      </c>
+      <c r="M53" s="4">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="N53" s="4">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="O53" s="4">
+        <v>16</v>
+      </c>
       <c r="P53" s="4"/>
     </row>
     <row r="54" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10622,16 +11635,38 @@
       <c r="E54" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
-      <c r="N54" s="4"/>
-      <c r="O54" s="4"/>
+      <c r="F54" s="4">
+        <v>0</v>
+      </c>
+      <c r="G54" s="4">
+        <v>1</v>
+      </c>
+      <c r="H54" s="4">
+        <v>2</v>
+      </c>
+      <c r="I54" s="4">
+        <v>1</v>
+      </c>
+      <c r="J54" s="4">
+        <v>3</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L54" s="4">
+        <v>25</v>
+      </c>
+      <c r="M54" s="4">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="N54" s="4">
+        <f t="shared" si="3"/>
+        <v>28.000000000000004</v>
+      </c>
+      <c r="O54" s="4">
+        <v>24</v>
+      </c>
       <c r="P54" s="4"/>
     </row>
     <row r="55" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10648,16 +11683,38 @@
       <c r="E55" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="4"/>
-      <c r="L55" s="4"/>
-      <c r="M55" s="4"/>
-      <c r="N55" s="4"/>
-      <c r="O55" s="4"/>
+      <c r="F55" s="4">
+        <v>1</v>
+      </c>
+      <c r="G55" s="4">
+        <v>5</v>
+      </c>
+      <c r="H55" s="4">
+        <v>1</v>
+      </c>
+      <c r="I55" s="4">
+        <v>1</v>
+      </c>
+      <c r="J55" s="4">
+        <v>1</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L55" s="4">
+        <v>25</v>
+      </c>
+      <c r="M55" s="4">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="N55" s="4">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="O55" s="4">
+        <v>22</v>
+      </c>
       <c r="P55" s="4"/>
     </row>
     <row r="56" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10674,16 +11731,38 @@
       <c r="E56" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4"/>
-      <c r="O56" s="4"/>
+      <c r="F56" s="4">
+        <v>0</v>
+      </c>
+      <c r="G56" s="4">
+        <v>3</v>
+      </c>
+      <c r="H56" s="4">
+        <v>5</v>
+      </c>
+      <c r="I56" s="4">
+        <v>2</v>
+      </c>
+      <c r="J56" s="4">
+        <v>0</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L56" s="4">
+        <v>25</v>
+      </c>
+      <c r="M56" s="4">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="N56" s="4">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="O56" s="4">
+        <v>22</v>
+      </c>
       <c r="P56" s="4"/>
     </row>
     <row r="57" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10700,16 +11779,38 @@
       <c r="E57" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
-      <c r="L57" s="4"/>
-      <c r="M57" s="4"/>
-      <c r="N57" s="4"/>
-      <c r="O57" s="4"/>
+      <c r="F57" s="4">
+        <v>2</v>
+      </c>
+      <c r="G57" s="4">
+        <v>1</v>
+      </c>
+      <c r="H57" s="4">
+        <v>1</v>
+      </c>
+      <c r="I57" s="4">
+        <v>2</v>
+      </c>
+      <c r="J57" s="4">
+        <v>1</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L57" s="4">
+        <v>25</v>
+      </c>
+      <c r="M57" s="4">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="N57" s="4">
+        <f t="shared" si="3"/>
+        <v>28.000000000000004</v>
+      </c>
+      <c r="O57" s="4">
+        <v>22</v>
+      </c>
       <c r="P57" s="4"/>
     </row>
     <row r="58" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10726,16 +11827,38 @@
       <c r="E58" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
-      <c r="L58" s="4"/>
-      <c r="M58" s="4"/>
-      <c r="N58" s="4"/>
-      <c r="O58" s="4"/>
+      <c r="F58" s="4">
+        <v>4</v>
+      </c>
+      <c r="G58" s="4">
+        <v>0</v>
+      </c>
+      <c r="H58" s="4">
+        <v>5</v>
+      </c>
+      <c r="I58" s="4">
+        <v>4</v>
+      </c>
+      <c r="J58" s="4">
+        <v>4</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L58" s="4">
+        <v>25</v>
+      </c>
+      <c r="M58" s="4">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="N58" s="4">
+        <f t="shared" si="3"/>
+        <v>68</v>
+      </c>
+      <c r="O58" s="4">
+        <v>24</v>
+      </c>
       <c r="P58" s="4"/>
     </row>
     <row r="59" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10752,16 +11875,38 @@
       <c r="E59" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="4"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="4"/>
-      <c r="L59" s="4"/>
-      <c r="M59" s="4"/>
-      <c r="N59" s="4"/>
-      <c r="O59" s="4"/>
+      <c r="F59" s="4">
+        <v>1</v>
+      </c>
+      <c r="G59" s="4">
+        <v>4</v>
+      </c>
+      <c r="H59" s="4">
+        <v>4</v>
+      </c>
+      <c r="I59" s="4">
+        <v>3</v>
+      </c>
+      <c r="J59" s="4">
+        <v>1</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L59" s="4">
+        <v>25</v>
+      </c>
+      <c r="M59" s="4">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="N59" s="4">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="O59" s="4">
+        <v>25</v>
+      </c>
       <c r="P59" s="4"/>
     </row>
     <row r="60" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10778,16 +11923,38 @@
       <c r="E60" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="4"/>
-      <c r="L60" s="4"/>
-      <c r="M60" s="4"/>
-      <c r="N60" s="4"/>
-      <c r="O60" s="4"/>
+      <c r="F60" s="4">
+        <v>2</v>
+      </c>
+      <c r="G60" s="4">
+        <v>4</v>
+      </c>
+      <c r="H60" s="4">
+        <v>5</v>
+      </c>
+      <c r="I60" s="4">
+        <v>1</v>
+      </c>
+      <c r="J60" s="4">
+        <v>1</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L60" s="4">
+        <v>25</v>
+      </c>
+      <c r="M60" s="4">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="N60" s="4">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="O60" s="4">
+        <v>25</v>
+      </c>
       <c r="P60" s="4"/>
     </row>
     <row r="61" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10804,16 +11971,38 @@
       <c r="E61" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
-      <c r="J61" s="4"/>
-      <c r="K61" s="4"/>
-      <c r="L61" s="4"/>
-      <c r="M61" s="4"/>
-      <c r="N61" s="4"/>
-      <c r="O61" s="4"/>
+      <c r="F61" s="4">
+        <v>0</v>
+      </c>
+      <c r="G61" s="4">
+        <v>4</v>
+      </c>
+      <c r="H61" s="4">
+        <v>5</v>
+      </c>
+      <c r="I61" s="4">
+        <v>4</v>
+      </c>
+      <c r="J61" s="4">
+        <v>4</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L61" s="4">
+        <v>25</v>
+      </c>
+      <c r="M61" s="4">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="N61" s="4">
+        <f t="shared" si="3"/>
+        <v>68</v>
+      </c>
+      <c r="O61" s="4">
+        <v>22</v>
+      </c>
       <c r="P61" s="4"/>
     </row>
     <row r="62" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10830,16 +12019,38 @@
       <c r="E62" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="4"/>
-      <c r="L62" s="4"/>
-      <c r="M62" s="4"/>
-      <c r="N62" s="4"/>
-      <c r="O62" s="4"/>
+      <c r="F62" s="4">
+        <v>2</v>
+      </c>
+      <c r="G62" s="4">
+        <v>5</v>
+      </c>
+      <c r="H62" s="4">
+        <v>5</v>
+      </c>
+      <c r="I62" s="4">
+        <v>4</v>
+      </c>
+      <c r="J62" s="4">
+        <v>4</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L62" s="4">
+        <v>25</v>
+      </c>
+      <c r="M62" s="4">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="N62" s="4">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="O62" s="4">
+        <v>23</v>
+      </c>
       <c r="P62" s="4"/>
     </row>
     <row r="63" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10856,16 +12067,38 @@
       <c r="E63" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="4"/>
-      <c r="L63" s="4"/>
-      <c r="M63" s="4"/>
-      <c r="N63" s="4"/>
-      <c r="O63" s="4"/>
+      <c r="F63" s="4">
+        <v>2</v>
+      </c>
+      <c r="G63" s="4">
+        <v>4</v>
+      </c>
+      <c r="H63" s="4">
+        <v>5</v>
+      </c>
+      <c r="I63" s="4">
+        <v>2</v>
+      </c>
+      <c r="J63" s="4">
+        <v>0</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L63" s="4">
+        <v>25</v>
+      </c>
+      <c r="M63" s="4">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="N63" s="4">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="O63" s="4">
+        <v>18</v>
+      </c>
       <c r="P63" s="4"/>
     </row>
   </sheetData>
